--- a/irb_submission/IRB_SUBMISSION_BUNDLE/03_SORA_Electronic_Data_Submission_Template.xlsx
+++ b/irb_submission/IRB_SUBMISSION_BUNDLE/03_SORA_Electronic_Data_Submission_Template.xlsx
@@ -2,8 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Entry" sheetId="1" r:id="R832e48333e924579"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="2" r:id="R53198b6615ac4562"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Entry" sheetId="1" r:id="R92ecf88bc42343e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="2" r:id="R563e1ce891b44394"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Site Summary" sheetId="3" r:id="R2f881b4ea8214977"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -210,7 +211,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="39">
+  <x:cellXfs count="41">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -243,10 +244,10 @@
     <x:xf numFmtId="200" fontId="0" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="200" fontId="0" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="0" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="0" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="201" fontId="0" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="0" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="201" fontId="0" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="0" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -264,6 +265,12 @@
     <x:xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -272,14 +279,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SoraDataTable" displayName="SoraDataTable" ref="A1:F401" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="6">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SoraDataTable" displayName="SoraDataTable" ref="A1:G401" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="7">
     <x:tableColumn id="1" name="site_code"/>
     <x:tableColumn id="2" name="clinic_row_id"/>
     <x:tableColumn id="3" name="sex"/>
-    <x:tableColumn id="4" name="age_at_onset_months"/>
-    <x:tableColumn id="5" name="dpre_days"/>
-    <x:tableColumn id="6" name="dpost_days"/>
+    <x:tableColumn id="4" name="age_at_onset_days"/>
+    <x:tableColumn id="5" name="vaccination_before_onset"/>
+    <x:tableColumn id="6" name="dpre_days"/>
+    <x:tableColumn id="7" name="dpost_days"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -484,8 +492,9 @@
     <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="12" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="23" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="26" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="16" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -499,12 +508,15 @@
         <x:v>sex</x:v>
       </x:c>
       <x:c r="D1" s="7" t="str">
-        <x:v>age_at_onset_months</x:v>
+        <x:v>age_at_onset_days</x:v>
       </x:c>
       <x:c r="E1" s="7" t="str">
+        <x:v>vaccination_before_onset</x:v>
+      </x:c>
+      <x:c r="F1" s="7" t="str">
         <x:v>dpre_days</x:v>
       </x:c>
-      <x:c r="F1" s="8" t="str">
+      <x:c r="G1" s="8" t="str">
         <x:v>dpost_days</x:v>
       </x:c>
     </x:row>
@@ -513,3218 +525,3621 @@
       <x:c r="B2" s="20"/>
       <x:c r="C2" s="11"/>
       <x:c r="D2" s="25"/>
-      <x:c r="E2" s="25"/>
-      <x:c r="F2" s="26"/>
+      <x:c r="E2" s="11"/>
+      <x:c r="F2" s="25"/>
+      <x:c r="G2" s="28"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="21"/>
       <x:c r="B3" s="22"/>
       <x:c r="C3" s="14"/>
-      <x:c r="D3" s="27"/>
-      <x:c r="E3" s="27"/>
-      <x:c r="F3" s="28"/>
+      <x:c r="D3" s="26"/>
+      <x:c r="E3" s="14"/>
+      <x:c r="F3" s="26"/>
+      <x:c r="G3" s="29"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="21"/>
       <x:c r="B4" s="22"/>
       <x:c r="C4" s="14"/>
-      <x:c r="D4" s="27"/>
-      <x:c r="E4" s="27"/>
-      <x:c r="F4" s="28"/>
+      <x:c r="D4" s="26"/>
+      <x:c r="E4" s="14"/>
+      <x:c r="F4" s="26"/>
+      <x:c r="G4" s="29"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="21"/>
       <x:c r="B5" s="22"/>
       <x:c r="C5" s="14"/>
-      <x:c r="D5" s="27"/>
-      <x:c r="E5" s="27"/>
-      <x:c r="F5" s="28"/>
+      <x:c r="D5" s="26"/>
+      <x:c r="E5" s="14"/>
+      <x:c r="F5" s="26"/>
+      <x:c r="G5" s="29"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="21"/>
       <x:c r="B6" s="22"/>
       <x:c r="C6" s="14"/>
-      <x:c r="D6" s="27"/>
-      <x:c r="E6" s="27"/>
-      <x:c r="F6" s="28"/>
+      <x:c r="D6" s="26"/>
+      <x:c r="E6" s="14"/>
+      <x:c r="F6" s="26"/>
+      <x:c r="G6" s="29"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="21"/>
       <x:c r="B7" s="22"/>
       <x:c r="C7" s="14"/>
-      <x:c r="D7" s="27"/>
-      <x:c r="E7" s="27"/>
-      <x:c r="F7" s="28"/>
+      <x:c r="D7" s="26"/>
+      <x:c r="E7" s="14"/>
+      <x:c r="F7" s="26"/>
+      <x:c r="G7" s="29"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="21"/>
       <x:c r="B8" s="22"/>
       <x:c r="C8" s="14"/>
-      <x:c r="D8" s="27"/>
-      <x:c r="E8" s="27"/>
-      <x:c r="F8" s="28"/>
+      <x:c r="D8" s="26"/>
+      <x:c r="E8" s="14"/>
+      <x:c r="F8" s="26"/>
+      <x:c r="G8" s="29"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="21"/>
       <x:c r="B9" s="22"/>
       <x:c r="C9" s="14"/>
-      <x:c r="D9" s="27"/>
-      <x:c r="E9" s="27"/>
-      <x:c r="F9" s="28"/>
+      <x:c r="D9" s="26"/>
+      <x:c r="E9" s="14"/>
+      <x:c r="F9" s="26"/>
+      <x:c r="G9" s="29"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="21"/>
       <x:c r="B10" s="22"/>
       <x:c r="C10" s="14"/>
-      <x:c r="D10" s="27"/>
-      <x:c r="E10" s="27"/>
-      <x:c r="F10" s="28"/>
+      <x:c r="D10" s="26"/>
+      <x:c r="E10" s="14"/>
+      <x:c r="F10" s="26"/>
+      <x:c r="G10" s="29"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="21"/>
       <x:c r="B11" s="22"/>
       <x:c r="C11" s="14"/>
-      <x:c r="D11" s="27"/>
-      <x:c r="E11" s="27"/>
-      <x:c r="F11" s="28"/>
+      <x:c r="D11" s="26"/>
+      <x:c r="E11" s="14"/>
+      <x:c r="F11" s="26"/>
+      <x:c r="G11" s="29"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="21"/>
       <x:c r="B12" s="22"/>
       <x:c r="C12" s="14"/>
-      <x:c r="D12" s="27"/>
-      <x:c r="E12" s="27"/>
-      <x:c r="F12" s="28"/>
+      <x:c r="D12" s="26"/>
+      <x:c r="E12" s="14"/>
+      <x:c r="F12" s="26"/>
+      <x:c r="G12" s="29"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="21"/>
       <x:c r="B13" s="22"/>
       <x:c r="C13" s="14"/>
-      <x:c r="D13" s="27"/>
-      <x:c r="E13" s="27"/>
-      <x:c r="F13" s="28"/>
+      <x:c r="D13" s="26"/>
+      <x:c r="E13" s="14"/>
+      <x:c r="F13" s="26"/>
+      <x:c r="G13" s="29"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="21"/>
       <x:c r="B14" s="22"/>
       <x:c r="C14" s="14"/>
-      <x:c r="D14" s="27"/>
-      <x:c r="E14" s="27"/>
-      <x:c r="F14" s="28"/>
+      <x:c r="D14" s="26"/>
+      <x:c r="E14" s="14"/>
+      <x:c r="F14" s="26"/>
+      <x:c r="G14" s="29"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="21"/>
       <x:c r="B15" s="22"/>
       <x:c r="C15" s="14"/>
-      <x:c r="D15" s="27"/>
-      <x:c r="E15" s="27"/>
-      <x:c r="F15" s="28"/>
+      <x:c r="D15" s="26"/>
+      <x:c r="E15" s="14"/>
+      <x:c r="F15" s="26"/>
+      <x:c r="G15" s="29"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="21"/>
       <x:c r="B16" s="22"/>
       <x:c r="C16" s="14"/>
-      <x:c r="D16" s="27"/>
-      <x:c r="E16" s="27"/>
-      <x:c r="F16" s="28"/>
+      <x:c r="D16" s="26"/>
+      <x:c r="E16" s="14"/>
+      <x:c r="F16" s="26"/>
+      <x:c r="G16" s="29"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="21"/>
       <x:c r="B17" s="22"/>
       <x:c r="C17" s="14"/>
-      <x:c r="D17" s="27"/>
-      <x:c r="E17" s="27"/>
-      <x:c r="F17" s="28"/>
+      <x:c r="D17" s="26"/>
+      <x:c r="E17" s="14"/>
+      <x:c r="F17" s="26"/>
+      <x:c r="G17" s="29"/>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="21"/>
       <x:c r="B18" s="22"/>
       <x:c r="C18" s="14"/>
-      <x:c r="D18" s="27"/>
-      <x:c r="E18" s="27"/>
-      <x:c r="F18" s="28"/>
+      <x:c r="D18" s="26"/>
+      <x:c r="E18" s="14"/>
+      <x:c r="F18" s="26"/>
+      <x:c r="G18" s="29"/>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="21"/>
       <x:c r="B19" s="22"/>
       <x:c r="C19" s="14"/>
-      <x:c r="D19" s="27"/>
-      <x:c r="E19" s="27"/>
-      <x:c r="F19" s="28"/>
+      <x:c r="D19" s="26"/>
+      <x:c r="E19" s="14"/>
+      <x:c r="F19" s="26"/>
+      <x:c r="G19" s="29"/>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="21"/>
       <x:c r="B20" s="22"/>
       <x:c r="C20" s="14"/>
-      <x:c r="D20" s="27"/>
-      <x:c r="E20" s="27"/>
-      <x:c r="F20" s="28"/>
+      <x:c r="D20" s="26"/>
+      <x:c r="E20" s="14"/>
+      <x:c r="F20" s="26"/>
+      <x:c r="G20" s="29"/>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="21"/>
       <x:c r="B21" s="22"/>
       <x:c r="C21" s="14"/>
-      <x:c r="D21" s="27"/>
-      <x:c r="E21" s="27"/>
-      <x:c r="F21" s="28"/>
+      <x:c r="D21" s="26"/>
+      <x:c r="E21" s="14"/>
+      <x:c r="F21" s="26"/>
+      <x:c r="G21" s="29"/>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="21"/>
       <x:c r="B22" s="22"/>
       <x:c r="C22" s="14"/>
-      <x:c r="D22" s="27"/>
-      <x:c r="E22" s="27"/>
-      <x:c r="F22" s="28"/>
+      <x:c r="D22" s="26"/>
+      <x:c r="E22" s="14"/>
+      <x:c r="F22" s="26"/>
+      <x:c r="G22" s="29"/>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="21"/>
       <x:c r="B23" s="22"/>
       <x:c r="C23" s="14"/>
-      <x:c r="D23" s="27"/>
-      <x:c r="E23" s="27"/>
-      <x:c r="F23" s="28"/>
+      <x:c r="D23" s="26"/>
+      <x:c r="E23" s="14"/>
+      <x:c r="F23" s="26"/>
+      <x:c r="G23" s="29"/>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="21"/>
       <x:c r="B24" s="22"/>
       <x:c r="C24" s="14"/>
-      <x:c r="D24" s="27"/>
-      <x:c r="E24" s="27"/>
-      <x:c r="F24" s="28"/>
+      <x:c r="D24" s="26"/>
+      <x:c r="E24" s="14"/>
+      <x:c r="F24" s="26"/>
+      <x:c r="G24" s="29"/>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="21"/>
       <x:c r="B25" s="22"/>
       <x:c r="C25" s="14"/>
-      <x:c r="D25" s="27"/>
-      <x:c r="E25" s="27"/>
-      <x:c r="F25" s="28"/>
+      <x:c r="D25" s="26"/>
+      <x:c r="E25" s="14"/>
+      <x:c r="F25" s="26"/>
+      <x:c r="G25" s="29"/>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="21"/>
       <x:c r="B26" s="22"/>
       <x:c r="C26" s="14"/>
-      <x:c r="D26" s="27"/>
-      <x:c r="E26" s="27"/>
-      <x:c r="F26" s="28"/>
+      <x:c r="D26" s="26"/>
+      <x:c r="E26" s="14"/>
+      <x:c r="F26" s="26"/>
+      <x:c r="G26" s="29"/>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="21"/>
       <x:c r="B27" s="22"/>
       <x:c r="C27" s="14"/>
-      <x:c r="D27" s="27"/>
-      <x:c r="E27" s="27"/>
-      <x:c r="F27" s="28"/>
+      <x:c r="D27" s="26"/>
+      <x:c r="E27" s="14"/>
+      <x:c r="F27" s="26"/>
+      <x:c r="G27" s="29"/>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="21"/>
       <x:c r="B28" s="22"/>
       <x:c r="C28" s="14"/>
-      <x:c r="D28" s="27"/>
-      <x:c r="E28" s="27"/>
-      <x:c r="F28" s="28"/>
+      <x:c r="D28" s="26"/>
+      <x:c r="E28" s="14"/>
+      <x:c r="F28" s="26"/>
+      <x:c r="G28" s="29"/>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="21"/>
       <x:c r="B29" s="22"/>
       <x:c r="C29" s="14"/>
-      <x:c r="D29" s="27"/>
-      <x:c r="E29" s="27"/>
-      <x:c r="F29" s="28"/>
+      <x:c r="D29" s="26"/>
+      <x:c r="E29" s="14"/>
+      <x:c r="F29" s="26"/>
+      <x:c r="G29" s="29"/>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="21"/>
       <x:c r="B30" s="22"/>
       <x:c r="C30" s="14"/>
-      <x:c r="D30" s="27"/>
-      <x:c r="E30" s="27"/>
-      <x:c r="F30" s="28"/>
+      <x:c r="D30" s="26"/>
+      <x:c r="E30" s="14"/>
+      <x:c r="F30" s="26"/>
+      <x:c r="G30" s="29"/>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="21"/>
       <x:c r="B31" s="22"/>
       <x:c r="C31" s="14"/>
-      <x:c r="D31" s="27"/>
-      <x:c r="E31" s="27"/>
-      <x:c r="F31" s="28"/>
+      <x:c r="D31" s="26"/>
+      <x:c r="E31" s="14"/>
+      <x:c r="F31" s="26"/>
+      <x:c r="G31" s="29"/>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="21"/>
       <x:c r="B32" s="22"/>
       <x:c r="C32" s="14"/>
-      <x:c r="D32" s="27"/>
-      <x:c r="E32" s="27"/>
-      <x:c r="F32" s="28"/>
+      <x:c r="D32" s="26"/>
+      <x:c r="E32" s="14"/>
+      <x:c r="F32" s="26"/>
+      <x:c r="G32" s="29"/>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="21"/>
       <x:c r="B33" s="22"/>
       <x:c r="C33" s="14"/>
-      <x:c r="D33" s="27"/>
-      <x:c r="E33" s="27"/>
-      <x:c r="F33" s="28"/>
+      <x:c r="D33" s="26"/>
+      <x:c r="E33" s="14"/>
+      <x:c r="F33" s="26"/>
+      <x:c r="G33" s="29"/>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="21"/>
       <x:c r="B34" s="22"/>
       <x:c r="C34" s="14"/>
-      <x:c r="D34" s="27"/>
-      <x:c r="E34" s="27"/>
-      <x:c r="F34" s="28"/>
+      <x:c r="D34" s="26"/>
+      <x:c r="E34" s="14"/>
+      <x:c r="F34" s="26"/>
+      <x:c r="G34" s="29"/>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="21"/>
       <x:c r="B35" s="22"/>
       <x:c r="C35" s="14"/>
-      <x:c r="D35" s="27"/>
-      <x:c r="E35" s="27"/>
-      <x:c r="F35" s="28"/>
+      <x:c r="D35" s="26"/>
+      <x:c r="E35" s="14"/>
+      <x:c r="F35" s="26"/>
+      <x:c r="G35" s="29"/>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="21"/>
       <x:c r="B36" s="22"/>
       <x:c r="C36" s="14"/>
-      <x:c r="D36" s="27"/>
-      <x:c r="E36" s="27"/>
-      <x:c r="F36" s="28"/>
+      <x:c r="D36" s="26"/>
+      <x:c r="E36" s="14"/>
+      <x:c r="F36" s="26"/>
+      <x:c r="G36" s="29"/>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="21"/>
       <x:c r="B37" s="22"/>
       <x:c r="C37" s="14"/>
-      <x:c r="D37" s="27"/>
-      <x:c r="E37" s="27"/>
-      <x:c r="F37" s="28"/>
+      <x:c r="D37" s="26"/>
+      <x:c r="E37" s="14"/>
+      <x:c r="F37" s="26"/>
+      <x:c r="G37" s="29"/>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="21"/>
       <x:c r="B38" s="22"/>
       <x:c r="C38" s="14"/>
-      <x:c r="D38" s="27"/>
-      <x:c r="E38" s="27"/>
-      <x:c r="F38" s="28"/>
+      <x:c r="D38" s="26"/>
+      <x:c r="E38" s="14"/>
+      <x:c r="F38" s="26"/>
+      <x:c r="G38" s="29"/>
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="21"/>
       <x:c r="B39" s="22"/>
       <x:c r="C39" s="14"/>
-      <x:c r="D39" s="27"/>
-      <x:c r="E39" s="27"/>
-      <x:c r="F39" s="28"/>
+      <x:c r="D39" s="26"/>
+      <x:c r="E39" s="14"/>
+      <x:c r="F39" s="26"/>
+      <x:c r="G39" s="29"/>
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="21"/>
       <x:c r="B40" s="22"/>
       <x:c r="C40" s="14"/>
-      <x:c r="D40" s="27"/>
-      <x:c r="E40" s="27"/>
-      <x:c r="F40" s="28"/>
+      <x:c r="D40" s="26"/>
+      <x:c r="E40" s="14"/>
+      <x:c r="F40" s="26"/>
+      <x:c r="G40" s="29"/>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="21"/>
       <x:c r="B41" s="22"/>
       <x:c r="C41" s="14"/>
-      <x:c r="D41" s="27"/>
-      <x:c r="E41" s="27"/>
-      <x:c r="F41" s="28"/>
+      <x:c r="D41" s="26"/>
+      <x:c r="E41" s="14"/>
+      <x:c r="F41" s="26"/>
+      <x:c r="G41" s="29"/>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="21"/>
       <x:c r="B42" s="22"/>
       <x:c r="C42" s="14"/>
-      <x:c r="D42" s="27"/>
-      <x:c r="E42" s="27"/>
-      <x:c r="F42" s="28"/>
+      <x:c r="D42" s="26"/>
+      <x:c r="E42" s="14"/>
+      <x:c r="F42" s="26"/>
+      <x:c r="G42" s="29"/>
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="21"/>
       <x:c r="B43" s="22"/>
       <x:c r="C43" s="14"/>
-      <x:c r="D43" s="27"/>
-      <x:c r="E43" s="27"/>
-      <x:c r="F43" s="28"/>
+      <x:c r="D43" s="26"/>
+      <x:c r="E43" s="14"/>
+      <x:c r="F43" s="26"/>
+      <x:c r="G43" s="29"/>
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="21"/>
       <x:c r="B44" s="22"/>
       <x:c r="C44" s="14"/>
-      <x:c r="D44" s="27"/>
-      <x:c r="E44" s="27"/>
-      <x:c r="F44" s="28"/>
+      <x:c r="D44" s="26"/>
+      <x:c r="E44" s="14"/>
+      <x:c r="F44" s="26"/>
+      <x:c r="G44" s="29"/>
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="21"/>
       <x:c r="B45" s="22"/>
       <x:c r="C45" s="14"/>
-      <x:c r="D45" s="27"/>
-      <x:c r="E45" s="27"/>
-      <x:c r="F45" s="28"/>
+      <x:c r="D45" s="26"/>
+      <x:c r="E45" s="14"/>
+      <x:c r="F45" s="26"/>
+      <x:c r="G45" s="29"/>
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="21"/>
       <x:c r="B46" s="22"/>
       <x:c r="C46" s="14"/>
-      <x:c r="D46" s="27"/>
-      <x:c r="E46" s="27"/>
-      <x:c r="F46" s="28"/>
+      <x:c r="D46" s="26"/>
+      <x:c r="E46" s="14"/>
+      <x:c r="F46" s="26"/>
+      <x:c r="G46" s="29"/>
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="21"/>
       <x:c r="B47" s="22"/>
       <x:c r="C47" s="14"/>
-      <x:c r="D47" s="27"/>
-      <x:c r="E47" s="27"/>
-      <x:c r="F47" s="28"/>
+      <x:c r="D47" s="26"/>
+      <x:c r="E47" s="14"/>
+      <x:c r="F47" s="26"/>
+      <x:c r="G47" s="29"/>
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="21"/>
       <x:c r="B48" s="22"/>
       <x:c r="C48" s="14"/>
-      <x:c r="D48" s="27"/>
-      <x:c r="E48" s="27"/>
-      <x:c r="F48" s="28"/>
+      <x:c r="D48" s="26"/>
+      <x:c r="E48" s="14"/>
+      <x:c r="F48" s="26"/>
+      <x:c r="G48" s="29"/>
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="21"/>
       <x:c r="B49" s="22"/>
       <x:c r="C49" s="14"/>
-      <x:c r="D49" s="27"/>
-      <x:c r="E49" s="27"/>
-      <x:c r="F49" s="28"/>
+      <x:c r="D49" s="26"/>
+      <x:c r="E49" s="14"/>
+      <x:c r="F49" s="26"/>
+      <x:c r="G49" s="29"/>
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="21"/>
       <x:c r="B50" s="22"/>
       <x:c r="C50" s="14"/>
-      <x:c r="D50" s="27"/>
-      <x:c r="E50" s="27"/>
-      <x:c r="F50" s="28"/>
+      <x:c r="D50" s="26"/>
+      <x:c r="E50" s="14"/>
+      <x:c r="F50" s="26"/>
+      <x:c r="G50" s="29"/>
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="21"/>
       <x:c r="B51" s="22"/>
       <x:c r="C51" s="14"/>
-      <x:c r="D51" s="27"/>
-      <x:c r="E51" s="27"/>
-      <x:c r="F51" s="28"/>
+      <x:c r="D51" s="26"/>
+      <x:c r="E51" s="14"/>
+      <x:c r="F51" s="26"/>
+      <x:c r="G51" s="29"/>
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="21"/>
       <x:c r="B52" s="22"/>
       <x:c r="C52" s="14"/>
-      <x:c r="D52" s="27"/>
-      <x:c r="E52" s="27"/>
-      <x:c r="F52" s="28"/>
+      <x:c r="D52" s="26"/>
+      <x:c r="E52" s="14"/>
+      <x:c r="F52" s="26"/>
+      <x:c r="G52" s="29"/>
     </x:row>
     <x:row r="53">
       <x:c r="A53" s="21"/>
       <x:c r="B53" s="22"/>
       <x:c r="C53" s="14"/>
-      <x:c r="D53" s="27"/>
-      <x:c r="E53" s="27"/>
-      <x:c r="F53" s="28"/>
+      <x:c r="D53" s="26"/>
+      <x:c r="E53" s="14"/>
+      <x:c r="F53" s="26"/>
+      <x:c r="G53" s="29"/>
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="21"/>
       <x:c r="B54" s="22"/>
       <x:c r="C54" s="14"/>
-      <x:c r="D54" s="27"/>
-      <x:c r="E54" s="27"/>
-      <x:c r="F54" s="28"/>
+      <x:c r="D54" s="26"/>
+      <x:c r="E54" s="14"/>
+      <x:c r="F54" s="26"/>
+      <x:c r="G54" s="29"/>
     </x:row>
     <x:row r="55">
       <x:c r="A55" s="21"/>
       <x:c r="B55" s="22"/>
       <x:c r="C55" s="14"/>
-      <x:c r="D55" s="27"/>
-      <x:c r="E55" s="27"/>
-      <x:c r="F55" s="28"/>
+      <x:c r="D55" s="26"/>
+      <x:c r="E55" s="14"/>
+      <x:c r="F55" s="26"/>
+      <x:c r="G55" s="29"/>
     </x:row>
     <x:row r="56">
       <x:c r="A56" s="21"/>
       <x:c r="B56" s="22"/>
       <x:c r="C56" s="14"/>
-      <x:c r="D56" s="27"/>
-      <x:c r="E56" s="27"/>
-      <x:c r="F56" s="28"/>
+      <x:c r="D56" s="26"/>
+      <x:c r="E56" s="14"/>
+      <x:c r="F56" s="26"/>
+      <x:c r="G56" s="29"/>
     </x:row>
     <x:row r="57">
       <x:c r="A57" s="21"/>
       <x:c r="B57" s="22"/>
       <x:c r="C57" s="14"/>
-      <x:c r="D57" s="27"/>
-      <x:c r="E57" s="27"/>
-      <x:c r="F57" s="28"/>
+      <x:c r="D57" s="26"/>
+      <x:c r="E57" s="14"/>
+      <x:c r="F57" s="26"/>
+      <x:c r="G57" s="29"/>
     </x:row>
     <x:row r="58">
       <x:c r="A58" s="21"/>
       <x:c r="B58" s="22"/>
       <x:c r="C58" s="14"/>
-      <x:c r="D58" s="27"/>
-      <x:c r="E58" s="27"/>
-      <x:c r="F58" s="28"/>
+      <x:c r="D58" s="26"/>
+      <x:c r="E58" s="14"/>
+      <x:c r="F58" s="26"/>
+      <x:c r="G58" s="29"/>
     </x:row>
     <x:row r="59">
       <x:c r="A59" s="21"/>
       <x:c r="B59" s="22"/>
       <x:c r="C59" s="14"/>
-      <x:c r="D59" s="27"/>
-      <x:c r="E59" s="27"/>
-      <x:c r="F59" s="28"/>
+      <x:c r="D59" s="26"/>
+      <x:c r="E59" s="14"/>
+      <x:c r="F59" s="26"/>
+      <x:c r="G59" s="29"/>
     </x:row>
     <x:row r="60">
       <x:c r="A60" s="21"/>
       <x:c r="B60" s="22"/>
       <x:c r="C60" s="14"/>
-      <x:c r="D60" s="27"/>
-      <x:c r="E60" s="27"/>
-      <x:c r="F60" s="28"/>
+      <x:c r="D60" s="26"/>
+      <x:c r="E60" s="14"/>
+      <x:c r="F60" s="26"/>
+      <x:c r="G60" s="29"/>
     </x:row>
     <x:row r="61">
       <x:c r="A61" s="21"/>
       <x:c r="B61" s="22"/>
       <x:c r="C61" s="14"/>
-      <x:c r="D61" s="27"/>
-      <x:c r="E61" s="27"/>
-      <x:c r="F61" s="28"/>
+      <x:c r="D61" s="26"/>
+      <x:c r="E61" s="14"/>
+      <x:c r="F61" s="26"/>
+      <x:c r="G61" s="29"/>
     </x:row>
     <x:row r="62">
       <x:c r="A62" s="21"/>
       <x:c r="B62" s="22"/>
       <x:c r="C62" s="14"/>
-      <x:c r="D62" s="27"/>
-      <x:c r="E62" s="27"/>
-      <x:c r="F62" s="28"/>
+      <x:c r="D62" s="26"/>
+      <x:c r="E62" s="14"/>
+      <x:c r="F62" s="26"/>
+      <x:c r="G62" s="29"/>
     </x:row>
     <x:row r="63">
       <x:c r="A63" s="21"/>
       <x:c r="B63" s="22"/>
       <x:c r="C63" s="14"/>
-      <x:c r="D63" s="27"/>
-      <x:c r="E63" s="27"/>
-      <x:c r="F63" s="28"/>
+      <x:c r="D63" s="26"/>
+      <x:c r="E63" s="14"/>
+      <x:c r="F63" s="26"/>
+      <x:c r="G63" s="29"/>
     </x:row>
     <x:row r="64">
       <x:c r="A64" s="21"/>
       <x:c r="B64" s="22"/>
       <x:c r="C64" s="14"/>
-      <x:c r="D64" s="27"/>
-      <x:c r="E64" s="27"/>
-      <x:c r="F64" s="28"/>
+      <x:c r="D64" s="26"/>
+      <x:c r="E64" s="14"/>
+      <x:c r="F64" s="26"/>
+      <x:c r="G64" s="29"/>
     </x:row>
     <x:row r="65">
       <x:c r="A65" s="21"/>
       <x:c r="B65" s="22"/>
       <x:c r="C65" s="14"/>
-      <x:c r="D65" s="27"/>
-      <x:c r="E65" s="27"/>
-      <x:c r="F65" s="28"/>
+      <x:c r="D65" s="26"/>
+      <x:c r="E65" s="14"/>
+      <x:c r="F65" s="26"/>
+      <x:c r="G65" s="29"/>
     </x:row>
     <x:row r="66">
       <x:c r="A66" s="21"/>
       <x:c r="B66" s="22"/>
       <x:c r="C66" s="14"/>
-      <x:c r="D66" s="27"/>
-      <x:c r="E66" s="27"/>
-      <x:c r="F66" s="28"/>
+      <x:c r="D66" s="26"/>
+      <x:c r="E66" s="14"/>
+      <x:c r="F66" s="26"/>
+      <x:c r="G66" s="29"/>
     </x:row>
     <x:row r="67">
       <x:c r="A67" s="21"/>
       <x:c r="B67" s="22"/>
       <x:c r="C67" s="14"/>
-      <x:c r="D67" s="27"/>
-      <x:c r="E67" s="27"/>
-      <x:c r="F67" s="28"/>
+      <x:c r="D67" s="26"/>
+      <x:c r="E67" s="14"/>
+      <x:c r="F67" s="26"/>
+      <x:c r="G67" s="29"/>
     </x:row>
     <x:row r="68">
       <x:c r="A68" s="21"/>
       <x:c r="B68" s="22"/>
       <x:c r="C68" s="14"/>
-      <x:c r="D68" s="27"/>
-      <x:c r="E68" s="27"/>
-      <x:c r="F68" s="28"/>
+      <x:c r="D68" s="26"/>
+      <x:c r="E68" s="14"/>
+      <x:c r="F68" s="26"/>
+      <x:c r="G68" s="29"/>
     </x:row>
     <x:row r="69">
       <x:c r="A69" s="21"/>
       <x:c r="B69" s="22"/>
       <x:c r="C69" s="14"/>
-      <x:c r="D69" s="27"/>
-      <x:c r="E69" s="27"/>
-      <x:c r="F69" s="28"/>
+      <x:c r="D69" s="26"/>
+      <x:c r="E69" s="14"/>
+      <x:c r="F69" s="26"/>
+      <x:c r="G69" s="29"/>
     </x:row>
     <x:row r="70">
       <x:c r="A70" s="21"/>
       <x:c r="B70" s="22"/>
       <x:c r="C70" s="14"/>
-      <x:c r="D70" s="27"/>
-      <x:c r="E70" s="27"/>
-      <x:c r="F70" s="28"/>
+      <x:c r="D70" s="26"/>
+      <x:c r="E70" s="14"/>
+      <x:c r="F70" s="26"/>
+      <x:c r="G70" s="29"/>
     </x:row>
     <x:row r="71">
       <x:c r="A71" s="21"/>
       <x:c r="B71" s="22"/>
       <x:c r="C71" s="14"/>
-      <x:c r="D71" s="27"/>
-      <x:c r="E71" s="27"/>
-      <x:c r="F71" s="28"/>
+      <x:c r="D71" s="26"/>
+      <x:c r="E71" s="14"/>
+      <x:c r="F71" s="26"/>
+      <x:c r="G71" s="29"/>
     </x:row>
     <x:row r="72">
       <x:c r="A72" s="21"/>
       <x:c r="B72" s="22"/>
       <x:c r="C72" s="14"/>
-      <x:c r="D72" s="27"/>
-      <x:c r="E72" s="27"/>
-      <x:c r="F72" s="28"/>
+      <x:c r="D72" s="26"/>
+      <x:c r="E72" s="14"/>
+      <x:c r="F72" s="26"/>
+      <x:c r="G72" s="29"/>
     </x:row>
     <x:row r="73">
       <x:c r="A73" s="21"/>
       <x:c r="B73" s="22"/>
       <x:c r="C73" s="14"/>
-      <x:c r="D73" s="27"/>
-      <x:c r="E73" s="27"/>
-      <x:c r="F73" s="28"/>
+      <x:c r="D73" s="26"/>
+      <x:c r="E73" s="14"/>
+      <x:c r="F73" s="26"/>
+      <x:c r="G73" s="29"/>
     </x:row>
     <x:row r="74">
       <x:c r="A74" s="21"/>
       <x:c r="B74" s="22"/>
       <x:c r="C74" s="14"/>
-      <x:c r="D74" s="27"/>
-      <x:c r="E74" s="27"/>
-      <x:c r="F74" s="28"/>
+      <x:c r="D74" s="26"/>
+      <x:c r="E74" s="14"/>
+      <x:c r="F74" s="26"/>
+      <x:c r="G74" s="29"/>
     </x:row>
     <x:row r="75">
       <x:c r="A75" s="21"/>
       <x:c r="B75" s="22"/>
       <x:c r="C75" s="14"/>
-      <x:c r="D75" s="27"/>
-      <x:c r="E75" s="27"/>
-      <x:c r="F75" s="28"/>
+      <x:c r="D75" s="26"/>
+      <x:c r="E75" s="14"/>
+      <x:c r="F75" s="26"/>
+      <x:c r="G75" s="29"/>
     </x:row>
     <x:row r="76">
       <x:c r="A76" s="21"/>
       <x:c r="B76" s="22"/>
       <x:c r="C76" s="14"/>
-      <x:c r="D76" s="27"/>
-      <x:c r="E76" s="27"/>
-      <x:c r="F76" s="28"/>
+      <x:c r="D76" s="26"/>
+      <x:c r="E76" s="14"/>
+      <x:c r="F76" s="26"/>
+      <x:c r="G76" s="29"/>
     </x:row>
     <x:row r="77">
       <x:c r="A77" s="21"/>
       <x:c r="B77" s="22"/>
       <x:c r="C77" s="14"/>
-      <x:c r="D77" s="27"/>
-      <x:c r="E77" s="27"/>
-      <x:c r="F77" s="28"/>
+      <x:c r="D77" s="26"/>
+      <x:c r="E77" s="14"/>
+      <x:c r="F77" s="26"/>
+      <x:c r="G77" s="29"/>
     </x:row>
     <x:row r="78">
       <x:c r="A78" s="21"/>
       <x:c r="B78" s="22"/>
       <x:c r="C78" s="14"/>
-      <x:c r="D78" s="27"/>
-      <x:c r="E78" s="27"/>
-      <x:c r="F78" s="28"/>
+      <x:c r="D78" s="26"/>
+      <x:c r="E78" s="14"/>
+      <x:c r="F78" s="26"/>
+      <x:c r="G78" s="29"/>
     </x:row>
     <x:row r="79">
       <x:c r="A79" s="21"/>
       <x:c r="B79" s="22"/>
       <x:c r="C79" s="14"/>
-      <x:c r="D79" s="27"/>
-      <x:c r="E79" s="27"/>
-      <x:c r="F79" s="28"/>
+      <x:c r="D79" s="26"/>
+      <x:c r="E79" s="14"/>
+      <x:c r="F79" s="26"/>
+      <x:c r="G79" s="29"/>
     </x:row>
     <x:row r="80">
       <x:c r="A80" s="21"/>
       <x:c r="B80" s="22"/>
       <x:c r="C80" s="14"/>
-      <x:c r="D80" s="27"/>
-      <x:c r="E80" s="27"/>
-      <x:c r="F80" s="28"/>
+      <x:c r="D80" s="26"/>
+      <x:c r="E80" s="14"/>
+      <x:c r="F80" s="26"/>
+      <x:c r="G80" s="29"/>
     </x:row>
     <x:row r="81">
       <x:c r="A81" s="21"/>
       <x:c r="B81" s="22"/>
       <x:c r="C81" s="14"/>
-      <x:c r="D81" s="27"/>
-      <x:c r="E81" s="27"/>
-      <x:c r="F81" s="28"/>
+      <x:c r="D81" s="26"/>
+      <x:c r="E81" s="14"/>
+      <x:c r="F81" s="26"/>
+      <x:c r="G81" s="29"/>
     </x:row>
     <x:row r="82">
       <x:c r="A82" s="21"/>
       <x:c r="B82" s="22"/>
       <x:c r="C82" s="14"/>
-      <x:c r="D82" s="27"/>
-      <x:c r="E82" s="27"/>
-      <x:c r="F82" s="28"/>
+      <x:c r="D82" s="26"/>
+      <x:c r="E82" s="14"/>
+      <x:c r="F82" s="26"/>
+      <x:c r="G82" s="29"/>
     </x:row>
     <x:row r="83">
       <x:c r="A83" s="21"/>
       <x:c r="B83" s="22"/>
       <x:c r="C83" s="14"/>
-      <x:c r="D83" s="27"/>
-      <x:c r="E83" s="27"/>
-      <x:c r="F83" s="28"/>
+      <x:c r="D83" s="26"/>
+      <x:c r="E83" s="14"/>
+      <x:c r="F83" s="26"/>
+      <x:c r="G83" s="29"/>
     </x:row>
     <x:row r="84">
       <x:c r="A84" s="21"/>
       <x:c r="B84" s="22"/>
       <x:c r="C84" s="14"/>
-      <x:c r="D84" s="27"/>
-      <x:c r="E84" s="27"/>
-      <x:c r="F84" s="28"/>
+      <x:c r="D84" s="26"/>
+      <x:c r="E84" s="14"/>
+      <x:c r="F84" s="26"/>
+      <x:c r="G84" s="29"/>
     </x:row>
     <x:row r="85">
       <x:c r="A85" s="21"/>
       <x:c r="B85" s="22"/>
       <x:c r="C85" s="14"/>
-      <x:c r="D85" s="27"/>
-      <x:c r="E85" s="27"/>
-      <x:c r="F85" s="28"/>
+      <x:c r="D85" s="26"/>
+      <x:c r="E85" s="14"/>
+      <x:c r="F85" s="26"/>
+      <x:c r="G85" s="29"/>
     </x:row>
     <x:row r="86">
       <x:c r="A86" s="21"/>
       <x:c r="B86" s="22"/>
       <x:c r="C86" s="14"/>
-      <x:c r="D86" s="27"/>
-      <x:c r="E86" s="27"/>
-      <x:c r="F86" s="28"/>
+      <x:c r="D86" s="26"/>
+      <x:c r="E86" s="14"/>
+      <x:c r="F86" s="26"/>
+      <x:c r="G86" s="29"/>
     </x:row>
     <x:row r="87">
       <x:c r="A87" s="21"/>
       <x:c r="B87" s="22"/>
       <x:c r="C87" s="14"/>
-      <x:c r="D87" s="27"/>
-      <x:c r="E87" s="27"/>
-      <x:c r="F87" s="28"/>
+      <x:c r="D87" s="26"/>
+      <x:c r="E87" s="14"/>
+      <x:c r="F87" s="26"/>
+      <x:c r="G87" s="29"/>
     </x:row>
     <x:row r="88">
       <x:c r="A88" s="21"/>
       <x:c r="B88" s="22"/>
       <x:c r="C88" s="14"/>
-      <x:c r="D88" s="27"/>
-      <x:c r="E88" s="27"/>
-      <x:c r="F88" s="28"/>
+      <x:c r="D88" s="26"/>
+      <x:c r="E88" s="14"/>
+      <x:c r="F88" s="26"/>
+      <x:c r="G88" s="29"/>
     </x:row>
     <x:row r="89">
       <x:c r="A89" s="21"/>
       <x:c r="B89" s="22"/>
       <x:c r="C89" s="14"/>
-      <x:c r="D89" s="27"/>
-      <x:c r="E89" s="27"/>
-      <x:c r="F89" s="28"/>
+      <x:c r="D89" s="26"/>
+      <x:c r="E89" s="14"/>
+      <x:c r="F89" s="26"/>
+      <x:c r="G89" s="29"/>
     </x:row>
     <x:row r="90">
       <x:c r="A90" s="21"/>
       <x:c r="B90" s="22"/>
       <x:c r="C90" s="14"/>
-      <x:c r="D90" s="27"/>
-      <x:c r="E90" s="27"/>
-      <x:c r="F90" s="28"/>
+      <x:c r="D90" s="26"/>
+      <x:c r="E90" s="14"/>
+      <x:c r="F90" s="26"/>
+      <x:c r="G90" s="29"/>
     </x:row>
     <x:row r="91">
       <x:c r="A91" s="21"/>
       <x:c r="B91" s="22"/>
       <x:c r="C91" s="14"/>
-      <x:c r="D91" s="27"/>
-      <x:c r="E91" s="27"/>
-      <x:c r="F91" s="28"/>
+      <x:c r="D91" s="26"/>
+      <x:c r="E91" s="14"/>
+      <x:c r="F91" s="26"/>
+      <x:c r="G91" s="29"/>
     </x:row>
     <x:row r="92">
       <x:c r="A92" s="21"/>
       <x:c r="B92" s="22"/>
       <x:c r="C92" s="14"/>
-      <x:c r="D92" s="27"/>
-      <x:c r="E92" s="27"/>
-      <x:c r="F92" s="28"/>
+      <x:c r="D92" s="26"/>
+      <x:c r="E92" s="14"/>
+      <x:c r="F92" s="26"/>
+      <x:c r="G92" s="29"/>
     </x:row>
     <x:row r="93">
       <x:c r="A93" s="21"/>
       <x:c r="B93" s="22"/>
       <x:c r="C93" s="14"/>
-      <x:c r="D93" s="27"/>
-      <x:c r="E93" s="27"/>
-      <x:c r="F93" s="28"/>
+      <x:c r="D93" s="26"/>
+      <x:c r="E93" s="14"/>
+      <x:c r="F93" s="26"/>
+      <x:c r="G93" s="29"/>
     </x:row>
     <x:row r="94">
       <x:c r="A94" s="21"/>
       <x:c r="B94" s="22"/>
       <x:c r="C94" s="14"/>
-      <x:c r="D94" s="27"/>
-      <x:c r="E94" s="27"/>
-      <x:c r="F94" s="28"/>
+      <x:c r="D94" s="26"/>
+      <x:c r="E94" s="14"/>
+      <x:c r="F94" s="26"/>
+      <x:c r="G94" s="29"/>
     </x:row>
     <x:row r="95">
       <x:c r="A95" s="21"/>
       <x:c r="B95" s="22"/>
       <x:c r="C95" s="14"/>
-      <x:c r="D95" s="27"/>
-      <x:c r="E95" s="27"/>
-      <x:c r="F95" s="28"/>
+      <x:c r="D95" s="26"/>
+      <x:c r="E95" s="14"/>
+      <x:c r="F95" s="26"/>
+      <x:c r="G95" s="29"/>
     </x:row>
     <x:row r="96">
       <x:c r="A96" s="21"/>
       <x:c r="B96" s="22"/>
       <x:c r="C96" s="14"/>
-      <x:c r="D96" s="27"/>
-      <x:c r="E96" s="27"/>
-      <x:c r="F96" s="28"/>
+      <x:c r="D96" s="26"/>
+      <x:c r="E96" s="14"/>
+      <x:c r="F96" s="26"/>
+      <x:c r="G96" s="29"/>
     </x:row>
     <x:row r="97">
       <x:c r="A97" s="21"/>
       <x:c r="B97" s="22"/>
       <x:c r="C97" s="14"/>
-      <x:c r="D97" s="27"/>
-      <x:c r="E97" s="27"/>
-      <x:c r="F97" s="28"/>
+      <x:c r="D97" s="26"/>
+      <x:c r="E97" s="14"/>
+      <x:c r="F97" s="26"/>
+      <x:c r="G97" s="29"/>
     </x:row>
     <x:row r="98">
       <x:c r="A98" s="21"/>
       <x:c r="B98" s="22"/>
       <x:c r="C98" s="14"/>
-      <x:c r="D98" s="27"/>
-      <x:c r="E98" s="27"/>
-      <x:c r="F98" s="28"/>
+      <x:c r="D98" s="26"/>
+      <x:c r="E98" s="14"/>
+      <x:c r="F98" s="26"/>
+      <x:c r="G98" s="29"/>
     </x:row>
     <x:row r="99">
       <x:c r="A99" s="21"/>
       <x:c r="B99" s="22"/>
       <x:c r="C99" s="14"/>
-      <x:c r="D99" s="27"/>
-      <x:c r="E99" s="27"/>
-      <x:c r="F99" s="28"/>
+      <x:c r="D99" s="26"/>
+      <x:c r="E99" s="14"/>
+      <x:c r="F99" s="26"/>
+      <x:c r="G99" s="29"/>
     </x:row>
     <x:row r="100">
       <x:c r="A100" s="21"/>
       <x:c r="B100" s="22"/>
       <x:c r="C100" s="14"/>
-      <x:c r="D100" s="27"/>
-      <x:c r="E100" s="27"/>
-      <x:c r="F100" s="28"/>
+      <x:c r="D100" s="26"/>
+      <x:c r="E100" s="14"/>
+      <x:c r="F100" s="26"/>
+      <x:c r="G100" s="29"/>
     </x:row>
     <x:row r="101">
       <x:c r="A101" s="21"/>
       <x:c r="B101" s="22"/>
       <x:c r="C101" s="14"/>
-      <x:c r="D101" s="27"/>
-      <x:c r="E101" s="27"/>
-      <x:c r="F101" s="28"/>
+      <x:c r="D101" s="26"/>
+      <x:c r="E101" s="14"/>
+      <x:c r="F101" s="26"/>
+      <x:c r="G101" s="29"/>
     </x:row>
     <x:row r="102">
       <x:c r="A102" s="21"/>
       <x:c r="B102" s="22"/>
       <x:c r="C102" s="14"/>
-      <x:c r="D102" s="27"/>
-      <x:c r="E102" s="27"/>
-      <x:c r="F102" s="28"/>
+      <x:c r="D102" s="26"/>
+      <x:c r="E102" s="14"/>
+      <x:c r="F102" s="26"/>
+      <x:c r="G102" s="29"/>
     </x:row>
     <x:row r="103">
       <x:c r="A103" s="21"/>
       <x:c r="B103" s="22"/>
       <x:c r="C103" s="14"/>
-      <x:c r="D103" s="27"/>
-      <x:c r="E103" s="27"/>
-      <x:c r="F103" s="28"/>
+      <x:c r="D103" s="26"/>
+      <x:c r="E103" s="14"/>
+      <x:c r="F103" s="26"/>
+      <x:c r="G103" s="29"/>
     </x:row>
     <x:row r="104">
       <x:c r="A104" s="21"/>
       <x:c r="B104" s="22"/>
       <x:c r="C104" s="14"/>
-      <x:c r="D104" s="27"/>
-      <x:c r="E104" s="27"/>
-      <x:c r="F104" s="28"/>
+      <x:c r="D104" s="26"/>
+      <x:c r="E104" s="14"/>
+      <x:c r="F104" s="26"/>
+      <x:c r="G104" s="29"/>
     </x:row>
     <x:row r="105">
       <x:c r="A105" s="21"/>
       <x:c r="B105" s="22"/>
       <x:c r="C105" s="14"/>
-      <x:c r="D105" s="27"/>
-      <x:c r="E105" s="27"/>
-      <x:c r="F105" s="28"/>
+      <x:c r="D105" s="26"/>
+      <x:c r="E105" s="14"/>
+      <x:c r="F105" s="26"/>
+      <x:c r="G105" s="29"/>
     </x:row>
     <x:row r="106">
       <x:c r="A106" s="21"/>
       <x:c r="B106" s="22"/>
       <x:c r="C106" s="14"/>
-      <x:c r="D106" s="27"/>
-      <x:c r="E106" s="27"/>
-      <x:c r="F106" s="28"/>
+      <x:c r="D106" s="26"/>
+      <x:c r="E106" s="14"/>
+      <x:c r="F106" s="26"/>
+      <x:c r="G106" s="29"/>
     </x:row>
     <x:row r="107">
       <x:c r="A107" s="21"/>
       <x:c r="B107" s="22"/>
       <x:c r="C107" s="14"/>
-      <x:c r="D107" s="27"/>
-      <x:c r="E107" s="27"/>
-      <x:c r="F107" s="28"/>
+      <x:c r="D107" s="26"/>
+      <x:c r="E107" s="14"/>
+      <x:c r="F107" s="26"/>
+      <x:c r="G107" s="29"/>
     </x:row>
     <x:row r="108">
       <x:c r="A108" s="21"/>
       <x:c r="B108" s="22"/>
       <x:c r="C108" s="14"/>
-      <x:c r="D108" s="27"/>
-      <x:c r="E108" s="27"/>
-      <x:c r="F108" s="28"/>
+      <x:c r="D108" s="26"/>
+      <x:c r="E108" s="14"/>
+      <x:c r="F108" s="26"/>
+      <x:c r="G108" s="29"/>
     </x:row>
     <x:row r="109">
       <x:c r="A109" s="21"/>
       <x:c r="B109" s="22"/>
       <x:c r="C109" s="14"/>
-      <x:c r="D109" s="27"/>
-      <x:c r="E109" s="27"/>
-      <x:c r="F109" s="28"/>
+      <x:c r="D109" s="26"/>
+      <x:c r="E109" s="14"/>
+      <x:c r="F109" s="26"/>
+      <x:c r="G109" s="29"/>
     </x:row>
     <x:row r="110">
       <x:c r="A110" s="21"/>
       <x:c r="B110" s="22"/>
       <x:c r="C110" s="14"/>
-      <x:c r="D110" s="27"/>
-      <x:c r="E110" s="27"/>
-      <x:c r="F110" s="28"/>
+      <x:c r="D110" s="26"/>
+      <x:c r="E110" s="14"/>
+      <x:c r="F110" s="26"/>
+      <x:c r="G110" s="29"/>
     </x:row>
     <x:row r="111">
       <x:c r="A111" s="21"/>
       <x:c r="B111" s="22"/>
       <x:c r="C111" s="14"/>
-      <x:c r="D111" s="27"/>
-      <x:c r="E111" s="27"/>
-      <x:c r="F111" s="28"/>
+      <x:c r="D111" s="26"/>
+      <x:c r="E111" s="14"/>
+      <x:c r="F111" s="26"/>
+      <x:c r="G111" s="29"/>
     </x:row>
     <x:row r="112">
       <x:c r="A112" s="21"/>
       <x:c r="B112" s="22"/>
       <x:c r="C112" s="14"/>
-      <x:c r="D112" s="27"/>
-      <x:c r="E112" s="27"/>
-      <x:c r="F112" s="28"/>
+      <x:c r="D112" s="26"/>
+      <x:c r="E112" s="14"/>
+      <x:c r="F112" s="26"/>
+      <x:c r="G112" s="29"/>
     </x:row>
     <x:row r="113">
       <x:c r="A113" s="21"/>
       <x:c r="B113" s="22"/>
       <x:c r="C113" s="14"/>
-      <x:c r="D113" s="27"/>
-      <x:c r="E113" s="27"/>
-      <x:c r="F113" s="28"/>
+      <x:c r="D113" s="26"/>
+      <x:c r="E113" s="14"/>
+      <x:c r="F113" s="26"/>
+      <x:c r="G113" s="29"/>
     </x:row>
     <x:row r="114">
       <x:c r="A114" s="21"/>
       <x:c r="B114" s="22"/>
       <x:c r="C114" s="14"/>
-      <x:c r="D114" s="27"/>
-      <x:c r="E114" s="27"/>
-      <x:c r="F114" s="28"/>
+      <x:c r="D114" s="26"/>
+      <x:c r="E114" s="14"/>
+      <x:c r="F114" s="26"/>
+      <x:c r="G114" s="29"/>
     </x:row>
     <x:row r="115">
       <x:c r="A115" s="21"/>
       <x:c r="B115" s="22"/>
       <x:c r="C115" s="14"/>
-      <x:c r="D115" s="27"/>
-      <x:c r="E115" s="27"/>
-      <x:c r="F115" s="28"/>
+      <x:c r="D115" s="26"/>
+      <x:c r="E115" s="14"/>
+      <x:c r="F115" s="26"/>
+      <x:c r="G115" s="29"/>
     </x:row>
     <x:row r="116">
       <x:c r="A116" s="21"/>
       <x:c r="B116" s="22"/>
       <x:c r="C116" s="14"/>
-      <x:c r="D116" s="27"/>
-      <x:c r="E116" s="27"/>
-      <x:c r="F116" s="28"/>
+      <x:c r="D116" s="26"/>
+      <x:c r="E116" s="14"/>
+      <x:c r="F116" s="26"/>
+      <x:c r="G116" s="29"/>
     </x:row>
     <x:row r="117">
       <x:c r="A117" s="21"/>
       <x:c r="B117" s="22"/>
       <x:c r="C117" s="14"/>
-      <x:c r="D117" s="27"/>
-      <x:c r="E117" s="27"/>
-      <x:c r="F117" s="28"/>
+      <x:c r="D117" s="26"/>
+      <x:c r="E117" s="14"/>
+      <x:c r="F117" s="26"/>
+      <x:c r="G117" s="29"/>
     </x:row>
     <x:row r="118">
       <x:c r="A118" s="21"/>
       <x:c r="B118" s="22"/>
       <x:c r="C118" s="14"/>
-      <x:c r="D118" s="27"/>
-      <x:c r="E118" s="27"/>
-      <x:c r="F118" s="28"/>
+      <x:c r="D118" s="26"/>
+      <x:c r="E118" s="14"/>
+      <x:c r="F118" s="26"/>
+      <x:c r="G118" s="29"/>
     </x:row>
     <x:row r="119">
       <x:c r="A119" s="21"/>
       <x:c r="B119" s="22"/>
       <x:c r="C119" s="14"/>
-      <x:c r="D119" s="27"/>
-      <x:c r="E119" s="27"/>
-      <x:c r="F119" s="28"/>
+      <x:c r="D119" s="26"/>
+      <x:c r="E119" s="14"/>
+      <x:c r="F119" s="26"/>
+      <x:c r="G119" s="29"/>
     </x:row>
     <x:row r="120">
       <x:c r="A120" s="21"/>
       <x:c r="B120" s="22"/>
       <x:c r="C120" s="14"/>
-      <x:c r="D120" s="27"/>
-      <x:c r="E120" s="27"/>
-      <x:c r="F120" s="28"/>
+      <x:c r="D120" s="26"/>
+      <x:c r="E120" s="14"/>
+      <x:c r="F120" s="26"/>
+      <x:c r="G120" s="29"/>
     </x:row>
     <x:row r="121">
       <x:c r="A121" s="21"/>
       <x:c r="B121" s="22"/>
       <x:c r="C121" s="14"/>
-      <x:c r="D121" s="27"/>
-      <x:c r="E121" s="27"/>
-      <x:c r="F121" s="28"/>
+      <x:c r="D121" s="26"/>
+      <x:c r="E121" s="14"/>
+      <x:c r="F121" s="26"/>
+      <x:c r="G121" s="29"/>
     </x:row>
     <x:row r="122">
       <x:c r="A122" s="21"/>
       <x:c r="B122" s="22"/>
       <x:c r="C122" s="14"/>
-      <x:c r="D122" s="27"/>
-      <x:c r="E122" s="27"/>
-      <x:c r="F122" s="28"/>
+      <x:c r="D122" s="26"/>
+      <x:c r="E122" s="14"/>
+      <x:c r="F122" s="26"/>
+      <x:c r="G122" s="29"/>
     </x:row>
     <x:row r="123">
       <x:c r="A123" s="21"/>
       <x:c r="B123" s="22"/>
       <x:c r="C123" s="14"/>
-      <x:c r="D123" s="27"/>
-      <x:c r="E123" s="27"/>
-      <x:c r="F123" s="28"/>
+      <x:c r="D123" s="26"/>
+      <x:c r="E123" s="14"/>
+      <x:c r="F123" s="26"/>
+      <x:c r="G123" s="29"/>
     </x:row>
     <x:row r="124">
       <x:c r="A124" s="21"/>
       <x:c r="B124" s="22"/>
       <x:c r="C124" s="14"/>
-      <x:c r="D124" s="27"/>
-      <x:c r="E124" s="27"/>
-      <x:c r="F124" s="28"/>
+      <x:c r="D124" s="26"/>
+      <x:c r="E124" s="14"/>
+      <x:c r="F124" s="26"/>
+      <x:c r="G124" s="29"/>
     </x:row>
     <x:row r="125">
       <x:c r="A125" s="21"/>
       <x:c r="B125" s="22"/>
       <x:c r="C125" s="14"/>
-      <x:c r="D125" s="27"/>
-      <x:c r="E125" s="27"/>
-      <x:c r="F125" s="28"/>
+      <x:c r="D125" s="26"/>
+      <x:c r="E125" s="14"/>
+      <x:c r="F125" s="26"/>
+      <x:c r="G125" s="29"/>
     </x:row>
     <x:row r="126">
       <x:c r="A126" s="21"/>
       <x:c r="B126" s="22"/>
       <x:c r="C126" s="14"/>
-      <x:c r="D126" s="27"/>
-      <x:c r="E126" s="27"/>
-      <x:c r="F126" s="28"/>
+      <x:c r="D126" s="26"/>
+      <x:c r="E126" s="14"/>
+      <x:c r="F126" s="26"/>
+      <x:c r="G126" s="29"/>
     </x:row>
     <x:row r="127">
       <x:c r="A127" s="21"/>
       <x:c r="B127" s="22"/>
       <x:c r="C127" s="14"/>
-      <x:c r="D127" s="27"/>
-      <x:c r="E127" s="27"/>
-      <x:c r="F127" s="28"/>
+      <x:c r="D127" s="26"/>
+      <x:c r="E127" s="14"/>
+      <x:c r="F127" s="26"/>
+      <x:c r="G127" s="29"/>
     </x:row>
     <x:row r="128">
       <x:c r="A128" s="21"/>
       <x:c r="B128" s="22"/>
       <x:c r="C128" s="14"/>
-      <x:c r="D128" s="27"/>
-      <x:c r="E128" s="27"/>
-      <x:c r="F128" s="28"/>
+      <x:c r="D128" s="26"/>
+      <x:c r="E128" s="14"/>
+      <x:c r="F128" s="26"/>
+      <x:c r="G128" s="29"/>
     </x:row>
     <x:row r="129">
       <x:c r="A129" s="21"/>
       <x:c r="B129" s="22"/>
       <x:c r="C129" s="14"/>
-      <x:c r="D129" s="27"/>
-      <x:c r="E129" s="27"/>
-      <x:c r="F129" s="28"/>
+      <x:c r="D129" s="26"/>
+      <x:c r="E129" s="14"/>
+      <x:c r="F129" s="26"/>
+      <x:c r="G129" s="29"/>
     </x:row>
     <x:row r="130">
       <x:c r="A130" s="21"/>
       <x:c r="B130" s="22"/>
       <x:c r="C130" s="14"/>
-      <x:c r="D130" s="27"/>
-      <x:c r="E130" s="27"/>
-      <x:c r="F130" s="28"/>
+      <x:c r="D130" s="26"/>
+      <x:c r="E130" s="14"/>
+      <x:c r="F130" s="26"/>
+      <x:c r="G130" s="29"/>
     </x:row>
     <x:row r="131">
       <x:c r="A131" s="21"/>
       <x:c r="B131" s="22"/>
       <x:c r="C131" s="14"/>
-      <x:c r="D131" s="27"/>
-      <x:c r="E131" s="27"/>
-      <x:c r="F131" s="28"/>
+      <x:c r="D131" s="26"/>
+      <x:c r="E131" s="14"/>
+      <x:c r="F131" s="26"/>
+      <x:c r="G131" s="29"/>
     </x:row>
     <x:row r="132">
       <x:c r="A132" s="21"/>
       <x:c r="B132" s="22"/>
       <x:c r="C132" s="14"/>
-      <x:c r="D132" s="27"/>
-      <x:c r="E132" s="27"/>
-      <x:c r="F132" s="28"/>
+      <x:c r="D132" s="26"/>
+      <x:c r="E132" s="14"/>
+      <x:c r="F132" s="26"/>
+      <x:c r="G132" s="29"/>
     </x:row>
     <x:row r="133">
       <x:c r="A133" s="21"/>
       <x:c r="B133" s="22"/>
       <x:c r="C133" s="14"/>
-      <x:c r="D133" s="27"/>
-      <x:c r="E133" s="27"/>
-      <x:c r="F133" s="28"/>
+      <x:c r="D133" s="26"/>
+      <x:c r="E133" s="14"/>
+      <x:c r="F133" s="26"/>
+      <x:c r="G133" s="29"/>
     </x:row>
     <x:row r="134">
       <x:c r="A134" s="21"/>
       <x:c r="B134" s="22"/>
       <x:c r="C134" s="14"/>
-      <x:c r="D134" s="27"/>
-      <x:c r="E134" s="27"/>
-      <x:c r="F134" s="28"/>
+      <x:c r="D134" s="26"/>
+      <x:c r="E134" s="14"/>
+      <x:c r="F134" s="26"/>
+      <x:c r="G134" s="29"/>
     </x:row>
     <x:row r="135">
       <x:c r="A135" s="21"/>
       <x:c r="B135" s="22"/>
       <x:c r="C135" s="14"/>
-      <x:c r="D135" s="27"/>
-      <x:c r="E135" s="27"/>
-      <x:c r="F135" s="28"/>
+      <x:c r="D135" s="26"/>
+      <x:c r="E135" s="14"/>
+      <x:c r="F135" s="26"/>
+      <x:c r="G135" s="29"/>
     </x:row>
     <x:row r="136">
       <x:c r="A136" s="21"/>
       <x:c r="B136" s="22"/>
       <x:c r="C136" s="14"/>
-      <x:c r="D136" s="27"/>
-      <x:c r="E136" s="27"/>
-      <x:c r="F136" s="28"/>
+      <x:c r="D136" s="26"/>
+      <x:c r="E136" s="14"/>
+      <x:c r="F136" s="26"/>
+      <x:c r="G136" s="29"/>
     </x:row>
     <x:row r="137">
       <x:c r="A137" s="21"/>
       <x:c r="B137" s="22"/>
       <x:c r="C137" s="14"/>
-      <x:c r="D137" s="27"/>
-      <x:c r="E137" s="27"/>
-      <x:c r="F137" s="28"/>
+      <x:c r="D137" s="26"/>
+      <x:c r="E137" s="14"/>
+      <x:c r="F137" s="26"/>
+      <x:c r="G137" s="29"/>
     </x:row>
     <x:row r="138">
       <x:c r="A138" s="21"/>
       <x:c r="B138" s="22"/>
       <x:c r="C138" s="14"/>
-      <x:c r="D138" s="27"/>
-      <x:c r="E138" s="27"/>
-      <x:c r="F138" s="28"/>
+      <x:c r="D138" s="26"/>
+      <x:c r="E138" s="14"/>
+      <x:c r="F138" s="26"/>
+      <x:c r="G138" s="29"/>
     </x:row>
     <x:row r="139">
       <x:c r="A139" s="21"/>
       <x:c r="B139" s="22"/>
       <x:c r="C139" s="14"/>
-      <x:c r="D139" s="27"/>
-      <x:c r="E139" s="27"/>
-      <x:c r="F139" s="28"/>
+      <x:c r="D139" s="26"/>
+      <x:c r="E139" s="14"/>
+      <x:c r="F139" s="26"/>
+      <x:c r="G139" s="29"/>
     </x:row>
     <x:row r="140">
       <x:c r="A140" s="21"/>
       <x:c r="B140" s="22"/>
       <x:c r="C140" s="14"/>
-      <x:c r="D140" s="27"/>
-      <x:c r="E140" s="27"/>
-      <x:c r="F140" s="28"/>
+      <x:c r="D140" s="26"/>
+      <x:c r="E140" s="14"/>
+      <x:c r="F140" s="26"/>
+      <x:c r="G140" s="29"/>
     </x:row>
     <x:row r="141">
       <x:c r="A141" s="21"/>
       <x:c r="B141" s="22"/>
       <x:c r="C141" s="14"/>
-      <x:c r="D141" s="27"/>
-      <x:c r="E141" s="27"/>
-      <x:c r="F141" s="28"/>
+      <x:c r="D141" s="26"/>
+      <x:c r="E141" s="14"/>
+      <x:c r="F141" s="26"/>
+      <x:c r="G141" s="29"/>
     </x:row>
     <x:row r="142">
       <x:c r="A142" s="21"/>
       <x:c r="B142" s="22"/>
       <x:c r="C142" s="14"/>
-      <x:c r="D142" s="27"/>
-      <x:c r="E142" s="27"/>
-      <x:c r="F142" s="28"/>
+      <x:c r="D142" s="26"/>
+      <x:c r="E142" s="14"/>
+      <x:c r="F142" s="26"/>
+      <x:c r="G142" s="29"/>
     </x:row>
     <x:row r="143">
       <x:c r="A143" s="21"/>
       <x:c r="B143" s="22"/>
       <x:c r="C143" s="14"/>
-      <x:c r="D143" s="27"/>
-      <x:c r="E143" s="27"/>
-      <x:c r="F143" s="28"/>
+      <x:c r="D143" s="26"/>
+      <x:c r="E143" s="14"/>
+      <x:c r="F143" s="26"/>
+      <x:c r="G143" s="29"/>
     </x:row>
     <x:row r="144">
       <x:c r="A144" s="21"/>
       <x:c r="B144" s="22"/>
       <x:c r="C144" s="14"/>
-      <x:c r="D144" s="27"/>
-      <x:c r="E144" s="27"/>
-      <x:c r="F144" s="28"/>
+      <x:c r="D144" s="26"/>
+      <x:c r="E144" s="14"/>
+      <x:c r="F144" s="26"/>
+      <x:c r="G144" s="29"/>
     </x:row>
     <x:row r="145">
       <x:c r="A145" s="21"/>
       <x:c r="B145" s="22"/>
       <x:c r="C145" s="14"/>
-      <x:c r="D145" s="27"/>
-      <x:c r="E145" s="27"/>
-      <x:c r="F145" s="28"/>
+      <x:c r="D145" s="26"/>
+      <x:c r="E145" s="14"/>
+      <x:c r="F145" s="26"/>
+      <x:c r="G145" s="29"/>
     </x:row>
     <x:row r="146">
       <x:c r="A146" s="21"/>
       <x:c r="B146" s="22"/>
       <x:c r="C146" s="14"/>
-      <x:c r="D146" s="27"/>
-      <x:c r="E146" s="27"/>
-      <x:c r="F146" s="28"/>
+      <x:c r="D146" s="26"/>
+      <x:c r="E146" s="14"/>
+      <x:c r="F146" s="26"/>
+      <x:c r="G146" s="29"/>
     </x:row>
     <x:row r="147">
       <x:c r="A147" s="21"/>
       <x:c r="B147" s="22"/>
       <x:c r="C147" s="14"/>
-      <x:c r="D147" s="27"/>
-      <x:c r="E147" s="27"/>
-      <x:c r="F147" s="28"/>
+      <x:c r="D147" s="26"/>
+      <x:c r="E147" s="14"/>
+      <x:c r="F147" s="26"/>
+      <x:c r="G147" s="29"/>
     </x:row>
     <x:row r="148">
       <x:c r="A148" s="21"/>
       <x:c r="B148" s="22"/>
       <x:c r="C148" s="14"/>
-      <x:c r="D148" s="27"/>
-      <x:c r="E148" s="27"/>
-      <x:c r="F148" s="28"/>
+      <x:c r="D148" s="26"/>
+      <x:c r="E148" s="14"/>
+      <x:c r="F148" s="26"/>
+      <x:c r="G148" s="29"/>
     </x:row>
     <x:row r="149">
       <x:c r="A149" s="21"/>
       <x:c r="B149" s="22"/>
       <x:c r="C149" s="14"/>
-      <x:c r="D149" s="27"/>
-      <x:c r="E149" s="27"/>
-      <x:c r="F149" s="28"/>
+      <x:c r="D149" s="26"/>
+      <x:c r="E149" s="14"/>
+      <x:c r="F149" s="26"/>
+      <x:c r="G149" s="29"/>
     </x:row>
     <x:row r="150">
       <x:c r="A150" s="21"/>
       <x:c r="B150" s="22"/>
       <x:c r="C150" s="14"/>
-      <x:c r="D150" s="27"/>
-      <x:c r="E150" s="27"/>
-      <x:c r="F150" s="28"/>
+      <x:c r="D150" s="26"/>
+      <x:c r="E150" s="14"/>
+      <x:c r="F150" s="26"/>
+      <x:c r="G150" s="29"/>
     </x:row>
     <x:row r="151">
       <x:c r="A151" s="21"/>
       <x:c r="B151" s="22"/>
       <x:c r="C151" s="14"/>
-      <x:c r="D151" s="27"/>
-      <x:c r="E151" s="27"/>
-      <x:c r="F151" s="28"/>
+      <x:c r="D151" s="26"/>
+      <x:c r="E151" s="14"/>
+      <x:c r="F151" s="26"/>
+      <x:c r="G151" s="29"/>
     </x:row>
     <x:row r="152">
       <x:c r="A152" s="21"/>
       <x:c r="B152" s="22"/>
       <x:c r="C152" s="14"/>
-      <x:c r="D152" s="27"/>
-      <x:c r="E152" s="27"/>
-      <x:c r="F152" s="28"/>
+      <x:c r="D152" s="26"/>
+      <x:c r="E152" s="14"/>
+      <x:c r="F152" s="26"/>
+      <x:c r="G152" s="29"/>
     </x:row>
     <x:row r="153">
       <x:c r="A153" s="21"/>
       <x:c r="B153" s="22"/>
       <x:c r="C153" s="14"/>
-      <x:c r="D153" s="27"/>
-      <x:c r="E153" s="27"/>
-      <x:c r="F153" s="28"/>
+      <x:c r="D153" s="26"/>
+      <x:c r="E153" s="14"/>
+      <x:c r="F153" s="26"/>
+      <x:c r="G153" s="29"/>
     </x:row>
     <x:row r="154">
       <x:c r="A154" s="21"/>
       <x:c r="B154" s="22"/>
       <x:c r="C154" s="14"/>
-      <x:c r="D154" s="27"/>
-      <x:c r="E154" s="27"/>
-      <x:c r="F154" s="28"/>
+      <x:c r="D154" s="26"/>
+      <x:c r="E154" s="14"/>
+      <x:c r="F154" s="26"/>
+      <x:c r="G154" s="29"/>
     </x:row>
     <x:row r="155">
       <x:c r="A155" s="21"/>
       <x:c r="B155" s="22"/>
       <x:c r="C155" s="14"/>
-      <x:c r="D155" s="27"/>
-      <x:c r="E155" s="27"/>
-      <x:c r="F155" s="28"/>
+      <x:c r="D155" s="26"/>
+      <x:c r="E155" s="14"/>
+      <x:c r="F155" s="26"/>
+      <x:c r="G155" s="29"/>
     </x:row>
     <x:row r="156">
       <x:c r="A156" s="21"/>
       <x:c r="B156" s="22"/>
       <x:c r="C156" s="14"/>
-      <x:c r="D156" s="27"/>
-      <x:c r="E156" s="27"/>
-      <x:c r="F156" s="28"/>
+      <x:c r="D156" s="26"/>
+      <x:c r="E156" s="14"/>
+      <x:c r="F156" s="26"/>
+      <x:c r="G156" s="29"/>
     </x:row>
     <x:row r="157">
       <x:c r="A157" s="21"/>
       <x:c r="B157" s="22"/>
       <x:c r="C157" s="14"/>
-      <x:c r="D157" s="27"/>
-      <x:c r="E157" s="27"/>
-      <x:c r="F157" s="28"/>
+      <x:c r="D157" s="26"/>
+      <x:c r="E157" s="14"/>
+      <x:c r="F157" s="26"/>
+      <x:c r="G157" s="29"/>
     </x:row>
     <x:row r="158">
       <x:c r="A158" s="21"/>
       <x:c r="B158" s="22"/>
       <x:c r="C158" s="14"/>
-      <x:c r="D158" s="27"/>
-      <x:c r="E158" s="27"/>
-      <x:c r="F158" s="28"/>
+      <x:c r="D158" s="26"/>
+      <x:c r="E158" s="14"/>
+      <x:c r="F158" s="26"/>
+      <x:c r="G158" s="29"/>
     </x:row>
     <x:row r="159">
       <x:c r="A159" s="21"/>
       <x:c r="B159" s="22"/>
       <x:c r="C159" s="14"/>
-      <x:c r="D159" s="27"/>
-      <x:c r="E159" s="27"/>
-      <x:c r="F159" s="28"/>
+      <x:c r="D159" s="26"/>
+      <x:c r="E159" s="14"/>
+      <x:c r="F159" s="26"/>
+      <x:c r="G159" s="29"/>
     </x:row>
     <x:row r="160">
       <x:c r="A160" s="21"/>
       <x:c r="B160" s="22"/>
       <x:c r="C160" s="14"/>
-      <x:c r="D160" s="27"/>
-      <x:c r="E160" s="27"/>
-      <x:c r="F160" s="28"/>
+      <x:c r="D160" s="26"/>
+      <x:c r="E160" s="14"/>
+      <x:c r="F160" s="26"/>
+      <x:c r="G160" s="29"/>
     </x:row>
     <x:row r="161">
       <x:c r="A161" s="21"/>
       <x:c r="B161" s="22"/>
       <x:c r="C161" s="14"/>
-      <x:c r="D161" s="27"/>
-      <x:c r="E161" s="27"/>
-      <x:c r="F161" s="28"/>
+      <x:c r="D161" s="26"/>
+      <x:c r="E161" s="14"/>
+      <x:c r="F161" s="26"/>
+      <x:c r="G161" s="29"/>
     </x:row>
     <x:row r="162">
       <x:c r="A162" s="21"/>
       <x:c r="B162" s="22"/>
       <x:c r="C162" s="14"/>
-      <x:c r="D162" s="27"/>
-      <x:c r="E162" s="27"/>
-      <x:c r="F162" s="28"/>
+      <x:c r="D162" s="26"/>
+      <x:c r="E162" s="14"/>
+      <x:c r="F162" s="26"/>
+      <x:c r="G162" s="29"/>
     </x:row>
     <x:row r="163">
       <x:c r="A163" s="21"/>
       <x:c r="B163" s="22"/>
       <x:c r="C163" s="14"/>
-      <x:c r="D163" s="27"/>
-      <x:c r="E163" s="27"/>
-      <x:c r="F163" s="28"/>
+      <x:c r="D163" s="26"/>
+      <x:c r="E163" s="14"/>
+      <x:c r="F163" s="26"/>
+      <x:c r="G163" s="29"/>
     </x:row>
     <x:row r="164">
       <x:c r="A164" s="21"/>
       <x:c r="B164" s="22"/>
       <x:c r="C164" s="14"/>
-      <x:c r="D164" s="27"/>
-      <x:c r="E164" s="27"/>
-      <x:c r="F164" s="28"/>
+      <x:c r="D164" s="26"/>
+      <x:c r="E164" s="14"/>
+      <x:c r="F164" s="26"/>
+      <x:c r="G164" s="29"/>
     </x:row>
     <x:row r="165">
       <x:c r="A165" s="21"/>
       <x:c r="B165" s="22"/>
       <x:c r="C165" s="14"/>
-      <x:c r="D165" s="27"/>
-      <x:c r="E165" s="27"/>
-      <x:c r="F165" s="28"/>
+      <x:c r="D165" s="26"/>
+      <x:c r="E165" s="14"/>
+      <x:c r="F165" s="26"/>
+      <x:c r="G165" s="29"/>
     </x:row>
     <x:row r="166">
       <x:c r="A166" s="21"/>
       <x:c r="B166" s="22"/>
       <x:c r="C166" s="14"/>
-      <x:c r="D166" s="27"/>
-      <x:c r="E166" s="27"/>
-      <x:c r="F166" s="28"/>
+      <x:c r="D166" s="26"/>
+      <x:c r="E166" s="14"/>
+      <x:c r="F166" s="26"/>
+      <x:c r="G166" s="29"/>
     </x:row>
     <x:row r="167">
       <x:c r="A167" s="21"/>
       <x:c r="B167" s="22"/>
       <x:c r="C167" s="14"/>
-      <x:c r="D167" s="27"/>
-      <x:c r="E167" s="27"/>
-      <x:c r="F167" s="28"/>
+      <x:c r="D167" s="26"/>
+      <x:c r="E167" s="14"/>
+      <x:c r="F167" s="26"/>
+      <x:c r="G167" s="29"/>
     </x:row>
     <x:row r="168">
       <x:c r="A168" s="21"/>
       <x:c r="B168" s="22"/>
       <x:c r="C168" s="14"/>
-      <x:c r="D168" s="27"/>
-      <x:c r="E168" s="27"/>
-      <x:c r="F168" s="28"/>
+      <x:c r="D168" s="26"/>
+      <x:c r="E168" s="14"/>
+      <x:c r="F168" s="26"/>
+      <x:c r="G168" s="29"/>
     </x:row>
     <x:row r="169">
       <x:c r="A169" s="21"/>
       <x:c r="B169" s="22"/>
       <x:c r="C169" s="14"/>
-      <x:c r="D169" s="27"/>
-      <x:c r="E169" s="27"/>
-      <x:c r="F169" s="28"/>
+      <x:c r="D169" s="26"/>
+      <x:c r="E169" s="14"/>
+      <x:c r="F169" s="26"/>
+      <x:c r="G169" s="29"/>
     </x:row>
     <x:row r="170">
       <x:c r="A170" s="21"/>
       <x:c r="B170" s="22"/>
       <x:c r="C170" s="14"/>
-      <x:c r="D170" s="27"/>
-      <x:c r="E170" s="27"/>
-      <x:c r="F170" s="28"/>
+      <x:c r="D170" s="26"/>
+      <x:c r="E170" s="14"/>
+      <x:c r="F170" s="26"/>
+      <x:c r="G170" s="29"/>
     </x:row>
     <x:row r="171">
       <x:c r="A171" s="21"/>
       <x:c r="B171" s="22"/>
       <x:c r="C171" s="14"/>
-      <x:c r="D171" s="27"/>
-      <x:c r="E171" s="27"/>
-      <x:c r="F171" s="28"/>
+      <x:c r="D171" s="26"/>
+      <x:c r="E171" s="14"/>
+      <x:c r="F171" s="26"/>
+      <x:c r="G171" s="29"/>
     </x:row>
     <x:row r="172">
       <x:c r="A172" s="21"/>
       <x:c r="B172" s="22"/>
       <x:c r="C172" s="14"/>
-      <x:c r="D172" s="27"/>
-      <x:c r="E172" s="27"/>
-      <x:c r="F172" s="28"/>
+      <x:c r="D172" s="26"/>
+      <x:c r="E172" s="14"/>
+      <x:c r="F172" s="26"/>
+      <x:c r="G172" s="29"/>
     </x:row>
     <x:row r="173">
       <x:c r="A173" s="21"/>
       <x:c r="B173" s="22"/>
       <x:c r="C173" s="14"/>
-      <x:c r="D173" s="27"/>
-      <x:c r="E173" s="27"/>
-      <x:c r="F173" s="28"/>
+      <x:c r="D173" s="26"/>
+      <x:c r="E173" s="14"/>
+      <x:c r="F173" s="26"/>
+      <x:c r="G173" s="29"/>
     </x:row>
     <x:row r="174">
       <x:c r="A174" s="21"/>
       <x:c r="B174" s="22"/>
       <x:c r="C174" s="14"/>
-      <x:c r="D174" s="27"/>
-      <x:c r="E174" s="27"/>
-      <x:c r="F174" s="28"/>
+      <x:c r="D174" s="26"/>
+      <x:c r="E174" s="14"/>
+      <x:c r="F174" s="26"/>
+      <x:c r="G174" s="29"/>
     </x:row>
     <x:row r="175">
       <x:c r="A175" s="21"/>
       <x:c r="B175" s="22"/>
       <x:c r="C175" s="14"/>
-      <x:c r="D175" s="27"/>
-      <x:c r="E175" s="27"/>
-      <x:c r="F175" s="28"/>
+      <x:c r="D175" s="26"/>
+      <x:c r="E175" s="14"/>
+      <x:c r="F175" s="26"/>
+      <x:c r="G175" s="29"/>
     </x:row>
     <x:row r="176">
       <x:c r="A176" s="21"/>
       <x:c r="B176" s="22"/>
       <x:c r="C176" s="14"/>
-      <x:c r="D176" s="27"/>
-      <x:c r="E176" s="27"/>
-      <x:c r="F176" s="28"/>
+      <x:c r="D176" s="26"/>
+      <x:c r="E176" s="14"/>
+      <x:c r="F176" s="26"/>
+      <x:c r="G176" s="29"/>
     </x:row>
     <x:row r="177">
       <x:c r="A177" s="21"/>
       <x:c r="B177" s="22"/>
       <x:c r="C177" s="14"/>
-      <x:c r="D177" s="27"/>
-      <x:c r="E177" s="27"/>
-      <x:c r="F177" s="28"/>
+      <x:c r="D177" s="26"/>
+      <x:c r="E177" s="14"/>
+      <x:c r="F177" s="26"/>
+      <x:c r="G177" s="29"/>
     </x:row>
     <x:row r="178">
       <x:c r="A178" s="21"/>
       <x:c r="B178" s="22"/>
       <x:c r="C178" s="14"/>
-      <x:c r="D178" s="27"/>
-      <x:c r="E178" s="27"/>
-      <x:c r="F178" s="28"/>
+      <x:c r="D178" s="26"/>
+      <x:c r="E178" s="14"/>
+      <x:c r="F178" s="26"/>
+      <x:c r="G178" s="29"/>
     </x:row>
     <x:row r="179">
       <x:c r="A179" s="21"/>
       <x:c r="B179" s="22"/>
       <x:c r="C179" s="14"/>
-      <x:c r="D179" s="27"/>
-      <x:c r="E179" s="27"/>
-      <x:c r="F179" s="28"/>
+      <x:c r="D179" s="26"/>
+      <x:c r="E179" s="14"/>
+      <x:c r="F179" s="26"/>
+      <x:c r="G179" s="29"/>
     </x:row>
     <x:row r="180">
       <x:c r="A180" s="21"/>
       <x:c r="B180" s="22"/>
       <x:c r="C180" s="14"/>
-      <x:c r="D180" s="27"/>
-      <x:c r="E180" s="27"/>
-      <x:c r="F180" s="28"/>
+      <x:c r="D180" s="26"/>
+      <x:c r="E180" s="14"/>
+      <x:c r="F180" s="26"/>
+      <x:c r="G180" s="29"/>
     </x:row>
     <x:row r="181">
       <x:c r="A181" s="21"/>
       <x:c r="B181" s="22"/>
       <x:c r="C181" s="14"/>
-      <x:c r="D181" s="27"/>
-      <x:c r="E181" s="27"/>
-      <x:c r="F181" s="28"/>
+      <x:c r="D181" s="26"/>
+      <x:c r="E181" s="14"/>
+      <x:c r="F181" s="26"/>
+      <x:c r="G181" s="29"/>
     </x:row>
     <x:row r="182">
       <x:c r="A182" s="21"/>
       <x:c r="B182" s="22"/>
       <x:c r="C182" s="14"/>
-      <x:c r="D182" s="27"/>
-      <x:c r="E182" s="27"/>
-      <x:c r="F182" s="28"/>
+      <x:c r="D182" s="26"/>
+      <x:c r="E182" s="14"/>
+      <x:c r="F182" s="26"/>
+      <x:c r="G182" s="29"/>
     </x:row>
     <x:row r="183">
       <x:c r="A183" s="21"/>
       <x:c r="B183" s="22"/>
       <x:c r="C183" s="14"/>
-      <x:c r="D183" s="27"/>
-      <x:c r="E183" s="27"/>
-      <x:c r="F183" s="28"/>
+      <x:c r="D183" s="26"/>
+      <x:c r="E183" s="14"/>
+      <x:c r="F183" s="26"/>
+      <x:c r="G183" s="29"/>
     </x:row>
     <x:row r="184">
       <x:c r="A184" s="21"/>
       <x:c r="B184" s="22"/>
       <x:c r="C184" s="14"/>
-      <x:c r="D184" s="27"/>
-      <x:c r="E184" s="27"/>
-      <x:c r="F184" s="28"/>
+      <x:c r="D184" s="26"/>
+      <x:c r="E184" s="14"/>
+      <x:c r="F184" s="26"/>
+      <x:c r="G184" s="29"/>
     </x:row>
     <x:row r="185">
       <x:c r="A185" s="21"/>
       <x:c r="B185" s="22"/>
       <x:c r="C185" s="14"/>
-      <x:c r="D185" s="27"/>
-      <x:c r="E185" s="27"/>
-      <x:c r="F185" s="28"/>
+      <x:c r="D185" s="26"/>
+      <x:c r="E185" s="14"/>
+      <x:c r="F185" s="26"/>
+      <x:c r="G185" s="29"/>
     </x:row>
     <x:row r="186">
       <x:c r="A186" s="21"/>
       <x:c r="B186" s="22"/>
       <x:c r="C186" s="14"/>
-      <x:c r="D186" s="27"/>
-      <x:c r="E186" s="27"/>
-      <x:c r="F186" s="28"/>
+      <x:c r="D186" s="26"/>
+      <x:c r="E186" s="14"/>
+      <x:c r="F186" s="26"/>
+      <x:c r="G186" s="29"/>
     </x:row>
     <x:row r="187">
       <x:c r="A187" s="21"/>
       <x:c r="B187" s="22"/>
       <x:c r="C187" s="14"/>
-      <x:c r="D187" s="27"/>
-      <x:c r="E187" s="27"/>
-      <x:c r="F187" s="28"/>
+      <x:c r="D187" s="26"/>
+      <x:c r="E187" s="14"/>
+      <x:c r="F187" s="26"/>
+      <x:c r="G187" s="29"/>
     </x:row>
     <x:row r="188">
       <x:c r="A188" s="21"/>
       <x:c r="B188" s="22"/>
       <x:c r="C188" s="14"/>
-      <x:c r="D188" s="27"/>
-      <x:c r="E188" s="27"/>
-      <x:c r="F188" s="28"/>
+      <x:c r="D188" s="26"/>
+      <x:c r="E188" s="14"/>
+      <x:c r="F188" s="26"/>
+      <x:c r="G188" s="29"/>
     </x:row>
     <x:row r="189">
       <x:c r="A189" s="21"/>
       <x:c r="B189" s="22"/>
       <x:c r="C189" s="14"/>
-      <x:c r="D189" s="27"/>
-      <x:c r="E189" s="27"/>
-      <x:c r="F189" s="28"/>
+      <x:c r="D189" s="26"/>
+      <x:c r="E189" s="14"/>
+      <x:c r="F189" s="26"/>
+      <x:c r="G189" s="29"/>
     </x:row>
     <x:row r="190">
       <x:c r="A190" s="21"/>
       <x:c r="B190" s="22"/>
       <x:c r="C190" s="14"/>
-      <x:c r="D190" s="27"/>
-      <x:c r="E190" s="27"/>
-      <x:c r="F190" s="28"/>
+      <x:c r="D190" s="26"/>
+      <x:c r="E190" s="14"/>
+      <x:c r="F190" s="26"/>
+      <x:c r="G190" s="29"/>
     </x:row>
     <x:row r="191">
       <x:c r="A191" s="21"/>
       <x:c r="B191" s="22"/>
       <x:c r="C191" s="14"/>
-      <x:c r="D191" s="27"/>
-      <x:c r="E191" s="27"/>
-      <x:c r="F191" s="28"/>
+      <x:c r="D191" s="26"/>
+      <x:c r="E191" s="14"/>
+      <x:c r="F191" s="26"/>
+      <x:c r="G191" s="29"/>
     </x:row>
     <x:row r="192">
       <x:c r="A192" s="21"/>
       <x:c r="B192" s="22"/>
       <x:c r="C192" s="14"/>
-      <x:c r="D192" s="27"/>
-      <x:c r="E192" s="27"/>
-      <x:c r="F192" s="28"/>
+      <x:c r="D192" s="26"/>
+      <x:c r="E192" s="14"/>
+      <x:c r="F192" s="26"/>
+      <x:c r="G192" s="29"/>
     </x:row>
     <x:row r="193">
       <x:c r="A193" s="21"/>
       <x:c r="B193" s="22"/>
       <x:c r="C193" s="14"/>
-      <x:c r="D193" s="27"/>
-      <x:c r="E193" s="27"/>
-      <x:c r="F193" s="28"/>
+      <x:c r="D193" s="26"/>
+      <x:c r="E193" s="14"/>
+      <x:c r="F193" s="26"/>
+      <x:c r="G193" s="29"/>
     </x:row>
     <x:row r="194">
       <x:c r="A194" s="21"/>
       <x:c r="B194" s="22"/>
       <x:c r="C194" s="14"/>
-      <x:c r="D194" s="27"/>
-      <x:c r="E194" s="27"/>
-      <x:c r="F194" s="28"/>
+      <x:c r="D194" s="26"/>
+      <x:c r="E194" s="14"/>
+      <x:c r="F194" s="26"/>
+      <x:c r="G194" s="29"/>
     </x:row>
     <x:row r="195">
       <x:c r="A195" s="21"/>
       <x:c r="B195" s="22"/>
       <x:c r="C195" s="14"/>
-      <x:c r="D195" s="27"/>
-      <x:c r="E195" s="27"/>
-      <x:c r="F195" s="28"/>
+      <x:c r="D195" s="26"/>
+      <x:c r="E195" s="14"/>
+      <x:c r="F195" s="26"/>
+      <x:c r="G195" s="29"/>
     </x:row>
     <x:row r="196">
       <x:c r="A196" s="21"/>
       <x:c r="B196" s="22"/>
       <x:c r="C196" s="14"/>
-      <x:c r="D196" s="27"/>
-      <x:c r="E196" s="27"/>
-      <x:c r="F196" s="28"/>
+      <x:c r="D196" s="26"/>
+      <x:c r="E196" s="14"/>
+      <x:c r="F196" s="26"/>
+      <x:c r="G196" s="29"/>
     </x:row>
     <x:row r="197">
       <x:c r="A197" s="21"/>
       <x:c r="B197" s="22"/>
       <x:c r="C197" s="14"/>
-      <x:c r="D197" s="27"/>
-      <x:c r="E197" s="27"/>
-      <x:c r="F197" s="28"/>
+      <x:c r="D197" s="26"/>
+      <x:c r="E197" s="14"/>
+      <x:c r="F197" s="26"/>
+      <x:c r="G197" s="29"/>
     </x:row>
     <x:row r="198">
       <x:c r="A198" s="21"/>
       <x:c r="B198" s="22"/>
       <x:c r="C198" s="14"/>
-      <x:c r="D198" s="27"/>
-      <x:c r="E198" s="27"/>
-      <x:c r="F198" s="28"/>
+      <x:c r="D198" s="26"/>
+      <x:c r="E198" s="14"/>
+      <x:c r="F198" s="26"/>
+      <x:c r="G198" s="29"/>
     </x:row>
     <x:row r="199">
       <x:c r="A199" s="21"/>
       <x:c r="B199" s="22"/>
       <x:c r="C199" s="14"/>
-      <x:c r="D199" s="27"/>
-      <x:c r="E199" s="27"/>
-      <x:c r="F199" s="28"/>
+      <x:c r="D199" s="26"/>
+      <x:c r="E199" s="14"/>
+      <x:c r="F199" s="26"/>
+      <x:c r="G199" s="29"/>
     </x:row>
     <x:row r="200">
       <x:c r="A200" s="21"/>
       <x:c r="B200" s="22"/>
       <x:c r="C200" s="14"/>
-      <x:c r="D200" s="27"/>
-      <x:c r="E200" s="27"/>
-      <x:c r="F200" s="28"/>
+      <x:c r="D200" s="26"/>
+      <x:c r="E200" s="14"/>
+      <x:c r="F200" s="26"/>
+      <x:c r="G200" s="29"/>
     </x:row>
     <x:row r="201">
       <x:c r="A201" s="21"/>
       <x:c r="B201" s="22"/>
       <x:c r="C201" s="14"/>
-      <x:c r="D201" s="27"/>
-      <x:c r="E201" s="27"/>
-      <x:c r="F201" s="28"/>
+      <x:c r="D201" s="26"/>
+      <x:c r="E201" s="14"/>
+      <x:c r="F201" s="26"/>
+      <x:c r="G201" s="29"/>
     </x:row>
     <x:row r="202">
       <x:c r="A202" s="21"/>
       <x:c r="B202" s="22"/>
       <x:c r="C202" s="14"/>
-      <x:c r="D202" s="27"/>
-      <x:c r="E202" s="27"/>
-      <x:c r="F202" s="28"/>
+      <x:c r="D202" s="26"/>
+      <x:c r="E202" s="14"/>
+      <x:c r="F202" s="26"/>
+      <x:c r="G202" s="29"/>
     </x:row>
     <x:row r="203">
       <x:c r="A203" s="21"/>
       <x:c r="B203" s="22"/>
       <x:c r="C203" s="14"/>
-      <x:c r="D203" s="27"/>
-      <x:c r="E203" s="27"/>
-      <x:c r="F203" s="28"/>
+      <x:c r="D203" s="26"/>
+      <x:c r="E203" s="14"/>
+      <x:c r="F203" s="26"/>
+      <x:c r="G203" s="29"/>
     </x:row>
     <x:row r="204">
       <x:c r="A204" s="21"/>
       <x:c r="B204" s="22"/>
       <x:c r="C204" s="14"/>
-      <x:c r="D204" s="27"/>
-      <x:c r="E204" s="27"/>
-      <x:c r="F204" s="28"/>
+      <x:c r="D204" s="26"/>
+      <x:c r="E204" s="14"/>
+      <x:c r="F204" s="26"/>
+      <x:c r="G204" s="29"/>
     </x:row>
     <x:row r="205">
       <x:c r="A205" s="21"/>
       <x:c r="B205" s="22"/>
       <x:c r="C205" s="14"/>
-      <x:c r="D205" s="27"/>
-      <x:c r="E205" s="27"/>
-      <x:c r="F205" s="28"/>
+      <x:c r="D205" s="26"/>
+      <x:c r="E205" s="14"/>
+      <x:c r="F205" s="26"/>
+      <x:c r="G205" s="29"/>
     </x:row>
     <x:row r="206">
       <x:c r="A206" s="21"/>
       <x:c r="B206" s="22"/>
       <x:c r="C206" s="14"/>
-      <x:c r="D206" s="27"/>
-      <x:c r="E206" s="27"/>
-      <x:c r="F206" s="28"/>
+      <x:c r="D206" s="26"/>
+      <x:c r="E206" s="14"/>
+      <x:c r="F206" s="26"/>
+      <x:c r="G206" s="29"/>
     </x:row>
     <x:row r="207">
       <x:c r="A207" s="21"/>
       <x:c r="B207" s="22"/>
       <x:c r="C207" s="14"/>
-      <x:c r="D207" s="27"/>
-      <x:c r="E207" s="27"/>
-      <x:c r="F207" s="28"/>
+      <x:c r="D207" s="26"/>
+      <x:c r="E207" s="14"/>
+      <x:c r="F207" s="26"/>
+      <x:c r="G207" s="29"/>
     </x:row>
     <x:row r="208">
       <x:c r="A208" s="21"/>
       <x:c r="B208" s="22"/>
       <x:c r="C208" s="14"/>
-      <x:c r="D208" s="27"/>
-      <x:c r="E208" s="27"/>
-      <x:c r="F208" s="28"/>
+      <x:c r="D208" s="26"/>
+      <x:c r="E208" s="14"/>
+      <x:c r="F208" s="26"/>
+      <x:c r="G208" s="29"/>
     </x:row>
     <x:row r="209">
       <x:c r="A209" s="21"/>
       <x:c r="B209" s="22"/>
       <x:c r="C209" s="14"/>
-      <x:c r="D209" s="27"/>
-      <x:c r="E209" s="27"/>
-      <x:c r="F209" s="28"/>
+      <x:c r="D209" s="26"/>
+      <x:c r="E209" s="14"/>
+      <x:c r="F209" s="26"/>
+      <x:c r="G209" s="29"/>
     </x:row>
     <x:row r="210">
       <x:c r="A210" s="21"/>
       <x:c r="B210" s="22"/>
       <x:c r="C210" s="14"/>
-      <x:c r="D210" s="27"/>
-      <x:c r="E210" s="27"/>
-      <x:c r="F210" s="28"/>
+      <x:c r="D210" s="26"/>
+      <x:c r="E210" s="14"/>
+      <x:c r="F210" s="26"/>
+      <x:c r="G210" s="29"/>
     </x:row>
     <x:row r="211">
       <x:c r="A211" s="21"/>
       <x:c r="B211" s="22"/>
       <x:c r="C211" s="14"/>
-      <x:c r="D211" s="27"/>
-      <x:c r="E211" s="27"/>
-      <x:c r="F211" s="28"/>
+      <x:c r="D211" s="26"/>
+      <x:c r="E211" s="14"/>
+      <x:c r="F211" s="26"/>
+      <x:c r="G211" s="29"/>
     </x:row>
     <x:row r="212">
       <x:c r="A212" s="21"/>
       <x:c r="B212" s="22"/>
       <x:c r="C212" s="14"/>
-      <x:c r="D212" s="27"/>
-      <x:c r="E212" s="27"/>
-      <x:c r="F212" s="28"/>
+      <x:c r="D212" s="26"/>
+      <x:c r="E212" s="14"/>
+      <x:c r="F212" s="26"/>
+      <x:c r="G212" s="29"/>
     </x:row>
     <x:row r="213">
       <x:c r="A213" s="21"/>
       <x:c r="B213" s="22"/>
       <x:c r="C213" s="14"/>
-      <x:c r="D213" s="27"/>
-      <x:c r="E213" s="27"/>
-      <x:c r="F213" s="28"/>
+      <x:c r="D213" s="26"/>
+      <x:c r="E213" s="14"/>
+      <x:c r="F213" s="26"/>
+      <x:c r="G213" s="29"/>
     </x:row>
     <x:row r="214">
       <x:c r="A214" s="21"/>
       <x:c r="B214" s="22"/>
       <x:c r="C214" s="14"/>
-      <x:c r="D214" s="27"/>
-      <x:c r="E214" s="27"/>
-      <x:c r="F214" s="28"/>
+      <x:c r="D214" s="26"/>
+      <x:c r="E214" s="14"/>
+      <x:c r="F214" s="26"/>
+      <x:c r="G214" s="29"/>
     </x:row>
     <x:row r="215">
       <x:c r="A215" s="21"/>
       <x:c r="B215" s="22"/>
       <x:c r="C215" s="14"/>
-      <x:c r="D215" s="27"/>
-      <x:c r="E215" s="27"/>
-      <x:c r="F215" s="28"/>
+      <x:c r="D215" s="26"/>
+      <x:c r="E215" s="14"/>
+      <x:c r="F215" s="26"/>
+      <x:c r="G215" s="29"/>
     </x:row>
     <x:row r="216">
       <x:c r="A216" s="21"/>
       <x:c r="B216" s="22"/>
       <x:c r="C216" s="14"/>
-      <x:c r="D216" s="27"/>
-      <x:c r="E216" s="27"/>
-      <x:c r="F216" s="28"/>
+      <x:c r="D216" s="26"/>
+      <x:c r="E216" s="14"/>
+      <x:c r="F216" s="26"/>
+      <x:c r="G216" s="29"/>
     </x:row>
     <x:row r="217">
       <x:c r="A217" s="21"/>
       <x:c r="B217" s="22"/>
       <x:c r="C217" s="14"/>
-      <x:c r="D217" s="27"/>
-      <x:c r="E217" s="27"/>
-      <x:c r="F217" s="28"/>
+      <x:c r="D217" s="26"/>
+      <x:c r="E217" s="14"/>
+      <x:c r="F217" s="26"/>
+      <x:c r="G217" s="29"/>
     </x:row>
     <x:row r="218">
       <x:c r="A218" s="21"/>
       <x:c r="B218" s="22"/>
       <x:c r="C218" s="14"/>
-      <x:c r="D218" s="27"/>
-      <x:c r="E218" s="27"/>
-      <x:c r="F218" s="28"/>
+      <x:c r="D218" s="26"/>
+      <x:c r="E218" s="14"/>
+      <x:c r="F218" s="26"/>
+      <x:c r="G218" s="29"/>
     </x:row>
     <x:row r="219">
       <x:c r="A219" s="21"/>
       <x:c r="B219" s="22"/>
       <x:c r="C219" s="14"/>
-      <x:c r="D219" s="27"/>
-      <x:c r="E219" s="27"/>
-      <x:c r="F219" s="28"/>
+      <x:c r="D219" s="26"/>
+      <x:c r="E219" s="14"/>
+      <x:c r="F219" s="26"/>
+      <x:c r="G219" s="29"/>
     </x:row>
     <x:row r="220">
       <x:c r="A220" s="21"/>
       <x:c r="B220" s="22"/>
       <x:c r="C220" s="14"/>
-      <x:c r="D220" s="27"/>
-      <x:c r="E220" s="27"/>
-      <x:c r="F220" s="28"/>
+      <x:c r="D220" s="26"/>
+      <x:c r="E220" s="14"/>
+      <x:c r="F220" s="26"/>
+      <x:c r="G220" s="29"/>
     </x:row>
     <x:row r="221">
       <x:c r="A221" s="21"/>
       <x:c r="B221" s="22"/>
       <x:c r="C221" s="14"/>
-      <x:c r="D221" s="27"/>
-      <x:c r="E221" s="27"/>
-      <x:c r="F221" s="28"/>
+      <x:c r="D221" s="26"/>
+      <x:c r="E221" s="14"/>
+      <x:c r="F221" s="26"/>
+      <x:c r="G221" s="29"/>
     </x:row>
     <x:row r="222">
       <x:c r="A222" s="21"/>
       <x:c r="B222" s="22"/>
       <x:c r="C222" s="14"/>
-      <x:c r="D222" s="27"/>
-      <x:c r="E222" s="27"/>
-      <x:c r="F222" s="28"/>
+      <x:c r="D222" s="26"/>
+      <x:c r="E222" s="14"/>
+      <x:c r="F222" s="26"/>
+      <x:c r="G222" s="29"/>
     </x:row>
     <x:row r="223">
       <x:c r="A223" s="21"/>
       <x:c r="B223" s="22"/>
       <x:c r="C223" s="14"/>
-      <x:c r="D223" s="27"/>
-      <x:c r="E223" s="27"/>
-      <x:c r="F223" s="28"/>
+      <x:c r="D223" s="26"/>
+      <x:c r="E223" s="14"/>
+      <x:c r="F223" s="26"/>
+      <x:c r="G223" s="29"/>
     </x:row>
     <x:row r="224">
       <x:c r="A224" s="21"/>
       <x:c r="B224" s="22"/>
       <x:c r="C224" s="14"/>
-      <x:c r="D224" s="27"/>
-      <x:c r="E224" s="27"/>
-      <x:c r="F224" s="28"/>
+      <x:c r="D224" s="26"/>
+      <x:c r="E224" s="14"/>
+      <x:c r="F224" s="26"/>
+      <x:c r="G224" s="29"/>
     </x:row>
     <x:row r="225">
       <x:c r="A225" s="21"/>
       <x:c r="B225" s="22"/>
       <x:c r="C225" s="14"/>
-      <x:c r="D225" s="27"/>
-      <x:c r="E225" s="27"/>
-      <x:c r="F225" s="28"/>
+      <x:c r="D225" s="26"/>
+      <x:c r="E225" s="14"/>
+      <x:c r="F225" s="26"/>
+      <x:c r="G225" s="29"/>
     </x:row>
     <x:row r="226">
       <x:c r="A226" s="21"/>
       <x:c r="B226" s="22"/>
       <x:c r="C226" s="14"/>
-      <x:c r="D226" s="27"/>
-      <x:c r="E226" s="27"/>
-      <x:c r="F226" s="28"/>
+      <x:c r="D226" s="26"/>
+      <x:c r="E226" s="14"/>
+      <x:c r="F226" s="26"/>
+      <x:c r="G226" s="29"/>
     </x:row>
     <x:row r="227">
       <x:c r="A227" s="21"/>
       <x:c r="B227" s="22"/>
       <x:c r="C227" s="14"/>
-      <x:c r="D227" s="27"/>
-      <x:c r="E227" s="27"/>
-      <x:c r="F227" s="28"/>
+      <x:c r="D227" s="26"/>
+      <x:c r="E227" s="14"/>
+      <x:c r="F227" s="26"/>
+      <x:c r="G227" s="29"/>
     </x:row>
     <x:row r="228">
       <x:c r="A228" s="21"/>
       <x:c r="B228" s="22"/>
       <x:c r="C228" s="14"/>
-      <x:c r="D228" s="27"/>
-      <x:c r="E228" s="27"/>
-      <x:c r="F228" s="28"/>
+      <x:c r="D228" s="26"/>
+      <x:c r="E228" s="14"/>
+      <x:c r="F228" s="26"/>
+      <x:c r="G228" s="29"/>
     </x:row>
     <x:row r="229">
       <x:c r="A229" s="21"/>
       <x:c r="B229" s="22"/>
       <x:c r="C229" s="14"/>
-      <x:c r="D229" s="27"/>
-      <x:c r="E229" s="27"/>
-      <x:c r="F229" s="28"/>
+      <x:c r="D229" s="26"/>
+      <x:c r="E229" s="14"/>
+      <x:c r="F229" s="26"/>
+      <x:c r="G229" s="29"/>
     </x:row>
     <x:row r="230">
       <x:c r="A230" s="21"/>
       <x:c r="B230" s="22"/>
       <x:c r="C230" s="14"/>
-      <x:c r="D230" s="27"/>
-      <x:c r="E230" s="27"/>
-      <x:c r="F230" s="28"/>
+      <x:c r="D230" s="26"/>
+      <x:c r="E230" s="14"/>
+      <x:c r="F230" s="26"/>
+      <x:c r="G230" s="29"/>
     </x:row>
     <x:row r="231">
       <x:c r="A231" s="21"/>
       <x:c r="B231" s="22"/>
       <x:c r="C231" s="14"/>
-      <x:c r="D231" s="27"/>
-      <x:c r="E231" s="27"/>
-      <x:c r="F231" s="28"/>
+      <x:c r="D231" s="26"/>
+      <x:c r="E231" s="14"/>
+      <x:c r="F231" s="26"/>
+      <x:c r="G231" s="29"/>
     </x:row>
     <x:row r="232">
       <x:c r="A232" s="21"/>
       <x:c r="B232" s="22"/>
       <x:c r="C232" s="14"/>
-      <x:c r="D232" s="27"/>
-      <x:c r="E232" s="27"/>
-      <x:c r="F232" s="28"/>
+      <x:c r="D232" s="26"/>
+      <x:c r="E232" s="14"/>
+      <x:c r="F232" s="26"/>
+      <x:c r="G232" s="29"/>
     </x:row>
     <x:row r="233">
       <x:c r="A233" s="21"/>
       <x:c r="B233" s="22"/>
       <x:c r="C233" s="14"/>
-      <x:c r="D233" s="27"/>
-      <x:c r="E233" s="27"/>
-      <x:c r="F233" s="28"/>
+      <x:c r="D233" s="26"/>
+      <x:c r="E233" s="14"/>
+      <x:c r="F233" s="26"/>
+      <x:c r="G233" s="29"/>
     </x:row>
     <x:row r="234">
       <x:c r="A234" s="21"/>
       <x:c r="B234" s="22"/>
       <x:c r="C234" s="14"/>
-      <x:c r="D234" s="27"/>
-      <x:c r="E234" s="27"/>
-      <x:c r="F234" s="28"/>
+      <x:c r="D234" s="26"/>
+      <x:c r="E234" s="14"/>
+      <x:c r="F234" s="26"/>
+      <x:c r="G234" s="29"/>
     </x:row>
     <x:row r="235">
       <x:c r="A235" s="21"/>
       <x:c r="B235" s="22"/>
       <x:c r="C235" s="14"/>
-      <x:c r="D235" s="27"/>
-      <x:c r="E235" s="27"/>
-      <x:c r="F235" s="28"/>
+      <x:c r="D235" s="26"/>
+      <x:c r="E235" s="14"/>
+      <x:c r="F235" s="26"/>
+      <x:c r="G235" s="29"/>
     </x:row>
     <x:row r="236">
       <x:c r="A236" s="21"/>
       <x:c r="B236" s="22"/>
       <x:c r="C236" s="14"/>
-      <x:c r="D236" s="27"/>
-      <x:c r="E236" s="27"/>
-      <x:c r="F236" s="28"/>
+      <x:c r="D236" s="26"/>
+      <x:c r="E236" s="14"/>
+      <x:c r="F236" s="26"/>
+      <x:c r="G236" s="29"/>
     </x:row>
     <x:row r="237">
       <x:c r="A237" s="21"/>
       <x:c r="B237" s="22"/>
       <x:c r="C237" s="14"/>
-      <x:c r="D237" s="27"/>
-      <x:c r="E237" s="27"/>
-      <x:c r="F237" s="28"/>
+      <x:c r="D237" s="26"/>
+      <x:c r="E237" s="14"/>
+      <x:c r="F237" s="26"/>
+      <x:c r="G237" s="29"/>
     </x:row>
     <x:row r="238">
       <x:c r="A238" s="21"/>
       <x:c r="B238" s="22"/>
       <x:c r="C238" s="14"/>
-      <x:c r="D238" s="27"/>
-      <x:c r="E238" s="27"/>
-      <x:c r="F238" s="28"/>
+      <x:c r="D238" s="26"/>
+      <x:c r="E238" s="14"/>
+      <x:c r="F238" s="26"/>
+      <x:c r="G238" s="29"/>
     </x:row>
     <x:row r="239">
       <x:c r="A239" s="21"/>
       <x:c r="B239" s="22"/>
       <x:c r="C239" s="14"/>
-      <x:c r="D239" s="27"/>
-      <x:c r="E239" s="27"/>
-      <x:c r="F239" s="28"/>
+      <x:c r="D239" s="26"/>
+      <x:c r="E239" s="14"/>
+      <x:c r="F239" s="26"/>
+      <x:c r="G239" s="29"/>
     </x:row>
     <x:row r="240">
       <x:c r="A240" s="21"/>
       <x:c r="B240" s="22"/>
       <x:c r="C240" s="14"/>
-      <x:c r="D240" s="27"/>
-      <x:c r="E240" s="27"/>
-      <x:c r="F240" s="28"/>
+      <x:c r="D240" s="26"/>
+      <x:c r="E240" s="14"/>
+      <x:c r="F240" s="26"/>
+      <x:c r="G240" s="29"/>
     </x:row>
     <x:row r="241">
       <x:c r="A241" s="21"/>
       <x:c r="B241" s="22"/>
       <x:c r="C241" s="14"/>
-      <x:c r="D241" s="27"/>
-      <x:c r="E241" s="27"/>
-      <x:c r="F241" s="28"/>
+      <x:c r="D241" s="26"/>
+      <x:c r="E241" s="14"/>
+      <x:c r="F241" s="26"/>
+      <x:c r="G241" s="29"/>
     </x:row>
     <x:row r="242">
       <x:c r="A242" s="21"/>
       <x:c r="B242" s="22"/>
       <x:c r="C242" s="14"/>
-      <x:c r="D242" s="27"/>
-      <x:c r="E242" s="27"/>
-      <x:c r="F242" s="28"/>
+      <x:c r="D242" s="26"/>
+      <x:c r="E242" s="14"/>
+      <x:c r="F242" s="26"/>
+      <x:c r="G242" s="29"/>
     </x:row>
     <x:row r="243">
       <x:c r="A243" s="21"/>
       <x:c r="B243" s="22"/>
       <x:c r="C243" s="14"/>
-      <x:c r="D243" s="27"/>
-      <x:c r="E243" s="27"/>
-      <x:c r="F243" s="28"/>
+      <x:c r="D243" s="26"/>
+      <x:c r="E243" s="14"/>
+      <x:c r="F243" s="26"/>
+      <x:c r="G243" s="29"/>
     </x:row>
     <x:row r="244">
       <x:c r="A244" s="21"/>
       <x:c r="B244" s="22"/>
       <x:c r="C244" s="14"/>
-      <x:c r="D244" s="27"/>
-      <x:c r="E244" s="27"/>
-      <x:c r="F244" s="28"/>
+      <x:c r="D244" s="26"/>
+      <x:c r="E244" s="14"/>
+      <x:c r="F244" s="26"/>
+      <x:c r="G244" s="29"/>
     </x:row>
     <x:row r="245">
       <x:c r="A245" s="21"/>
       <x:c r="B245" s="22"/>
       <x:c r="C245" s="14"/>
-      <x:c r="D245" s="27"/>
-      <x:c r="E245" s="27"/>
-      <x:c r="F245" s="28"/>
+      <x:c r="D245" s="26"/>
+      <x:c r="E245" s="14"/>
+      <x:c r="F245" s="26"/>
+      <x:c r="G245" s="29"/>
     </x:row>
     <x:row r="246">
       <x:c r="A246" s="21"/>
       <x:c r="B246" s="22"/>
       <x:c r="C246" s="14"/>
-      <x:c r="D246" s="27"/>
-      <x:c r="E246" s="27"/>
-      <x:c r="F246" s="28"/>
+      <x:c r="D246" s="26"/>
+      <x:c r="E246" s="14"/>
+      <x:c r="F246" s="26"/>
+      <x:c r="G246" s="29"/>
     </x:row>
     <x:row r="247">
       <x:c r="A247" s="21"/>
       <x:c r="B247" s="22"/>
       <x:c r="C247" s="14"/>
-      <x:c r="D247" s="27"/>
-      <x:c r="E247" s="27"/>
-      <x:c r="F247" s="28"/>
+      <x:c r="D247" s="26"/>
+      <x:c r="E247" s="14"/>
+      <x:c r="F247" s="26"/>
+      <x:c r="G247" s="29"/>
     </x:row>
     <x:row r="248">
       <x:c r="A248" s="21"/>
       <x:c r="B248" s="22"/>
       <x:c r="C248" s="14"/>
-      <x:c r="D248" s="27"/>
-      <x:c r="E248" s="27"/>
-      <x:c r="F248" s="28"/>
+      <x:c r="D248" s="26"/>
+      <x:c r="E248" s="14"/>
+      <x:c r="F248" s="26"/>
+      <x:c r="G248" s="29"/>
     </x:row>
     <x:row r="249">
       <x:c r="A249" s="21"/>
       <x:c r="B249" s="22"/>
       <x:c r="C249" s="14"/>
-      <x:c r="D249" s="27"/>
-      <x:c r="E249" s="27"/>
-      <x:c r="F249" s="28"/>
+      <x:c r="D249" s="26"/>
+      <x:c r="E249" s="14"/>
+      <x:c r="F249" s="26"/>
+      <x:c r="G249" s="29"/>
     </x:row>
     <x:row r="250">
       <x:c r="A250" s="21"/>
       <x:c r="B250" s="22"/>
       <x:c r="C250" s="14"/>
-      <x:c r="D250" s="27"/>
-      <x:c r="E250" s="27"/>
-      <x:c r="F250" s="28"/>
+      <x:c r="D250" s="26"/>
+      <x:c r="E250" s="14"/>
+      <x:c r="F250" s="26"/>
+      <x:c r="G250" s="29"/>
     </x:row>
     <x:row r="251">
       <x:c r="A251" s="21"/>
       <x:c r="B251" s="22"/>
       <x:c r="C251" s="14"/>
-      <x:c r="D251" s="27"/>
-      <x:c r="E251" s="27"/>
-      <x:c r="F251" s="28"/>
+      <x:c r="D251" s="26"/>
+      <x:c r="E251" s="14"/>
+      <x:c r="F251" s="26"/>
+      <x:c r="G251" s="29"/>
     </x:row>
     <x:row r="252">
       <x:c r="A252" s="21"/>
       <x:c r="B252" s="22"/>
       <x:c r="C252" s="14"/>
-      <x:c r="D252" s="27"/>
-      <x:c r="E252" s="27"/>
-      <x:c r="F252" s="28"/>
+      <x:c r="D252" s="26"/>
+      <x:c r="E252" s="14"/>
+      <x:c r="F252" s="26"/>
+      <x:c r="G252" s="29"/>
     </x:row>
     <x:row r="253">
       <x:c r="A253" s="21"/>
       <x:c r="B253" s="22"/>
       <x:c r="C253" s="14"/>
-      <x:c r="D253" s="27"/>
-      <x:c r="E253" s="27"/>
-      <x:c r="F253" s="28"/>
+      <x:c r="D253" s="26"/>
+      <x:c r="E253" s="14"/>
+      <x:c r="F253" s="26"/>
+      <x:c r="G253" s="29"/>
     </x:row>
     <x:row r="254">
       <x:c r="A254" s="21"/>
       <x:c r="B254" s="22"/>
       <x:c r="C254" s="14"/>
-      <x:c r="D254" s="27"/>
-      <x:c r="E254" s="27"/>
-      <x:c r="F254" s="28"/>
+      <x:c r="D254" s="26"/>
+      <x:c r="E254" s="14"/>
+      <x:c r="F254" s="26"/>
+      <x:c r="G254" s="29"/>
     </x:row>
     <x:row r="255">
       <x:c r="A255" s="21"/>
       <x:c r="B255" s="22"/>
       <x:c r="C255" s="14"/>
-      <x:c r="D255" s="27"/>
-      <x:c r="E255" s="27"/>
-      <x:c r="F255" s="28"/>
+      <x:c r="D255" s="26"/>
+      <x:c r="E255" s="14"/>
+      <x:c r="F255" s="26"/>
+      <x:c r="G255" s="29"/>
     </x:row>
     <x:row r="256">
       <x:c r="A256" s="21"/>
       <x:c r="B256" s="22"/>
       <x:c r="C256" s="14"/>
-      <x:c r="D256" s="27"/>
-      <x:c r="E256" s="27"/>
-      <x:c r="F256" s="28"/>
+      <x:c r="D256" s="26"/>
+      <x:c r="E256" s="14"/>
+      <x:c r="F256" s="26"/>
+      <x:c r="G256" s="29"/>
     </x:row>
     <x:row r="257">
       <x:c r="A257" s="21"/>
       <x:c r="B257" s="22"/>
       <x:c r="C257" s="14"/>
-      <x:c r="D257" s="27"/>
-      <x:c r="E257" s="27"/>
-      <x:c r="F257" s="28"/>
+      <x:c r="D257" s="26"/>
+      <x:c r="E257" s="14"/>
+      <x:c r="F257" s="26"/>
+      <x:c r="G257" s="29"/>
     </x:row>
     <x:row r="258">
       <x:c r="A258" s="21"/>
       <x:c r="B258" s="22"/>
       <x:c r="C258" s="14"/>
-      <x:c r="D258" s="27"/>
-      <x:c r="E258" s="27"/>
-      <x:c r="F258" s="28"/>
+      <x:c r="D258" s="26"/>
+      <x:c r="E258" s="14"/>
+      <x:c r="F258" s="26"/>
+      <x:c r="G258" s="29"/>
     </x:row>
     <x:row r="259">
       <x:c r="A259" s="21"/>
       <x:c r="B259" s="22"/>
       <x:c r="C259" s="14"/>
-      <x:c r="D259" s="27"/>
-      <x:c r="E259" s="27"/>
-      <x:c r="F259" s="28"/>
+      <x:c r="D259" s="26"/>
+      <x:c r="E259" s="14"/>
+      <x:c r="F259" s="26"/>
+      <x:c r="G259" s="29"/>
     </x:row>
     <x:row r="260">
       <x:c r="A260" s="21"/>
       <x:c r="B260" s="22"/>
       <x:c r="C260" s="14"/>
-      <x:c r="D260" s="27"/>
-      <x:c r="E260" s="27"/>
-      <x:c r="F260" s="28"/>
+      <x:c r="D260" s="26"/>
+      <x:c r="E260" s="14"/>
+      <x:c r="F260" s="26"/>
+      <x:c r="G260" s="29"/>
     </x:row>
     <x:row r="261">
       <x:c r="A261" s="21"/>
       <x:c r="B261" s="22"/>
       <x:c r="C261" s="14"/>
-      <x:c r="D261" s="27"/>
-      <x:c r="E261" s="27"/>
-      <x:c r="F261" s="28"/>
+      <x:c r="D261" s="26"/>
+      <x:c r="E261" s="14"/>
+      <x:c r="F261" s="26"/>
+      <x:c r="G261" s="29"/>
     </x:row>
     <x:row r="262">
       <x:c r="A262" s="21"/>
       <x:c r="B262" s="22"/>
       <x:c r="C262" s="14"/>
-      <x:c r="D262" s="27"/>
-      <x:c r="E262" s="27"/>
-      <x:c r="F262" s="28"/>
+      <x:c r="D262" s="26"/>
+      <x:c r="E262" s="14"/>
+      <x:c r="F262" s="26"/>
+      <x:c r="G262" s="29"/>
     </x:row>
     <x:row r="263">
       <x:c r="A263" s="21"/>
       <x:c r="B263" s="22"/>
       <x:c r="C263" s="14"/>
-      <x:c r="D263" s="27"/>
-      <x:c r="E263" s="27"/>
-      <x:c r="F263" s="28"/>
+      <x:c r="D263" s="26"/>
+      <x:c r="E263" s="14"/>
+      <x:c r="F263" s="26"/>
+      <x:c r="G263" s="29"/>
     </x:row>
     <x:row r="264">
       <x:c r="A264" s="21"/>
       <x:c r="B264" s="22"/>
       <x:c r="C264" s="14"/>
-      <x:c r="D264" s="27"/>
-      <x:c r="E264" s="27"/>
-      <x:c r="F264" s="28"/>
+      <x:c r="D264" s="26"/>
+      <x:c r="E264" s="14"/>
+      <x:c r="F264" s="26"/>
+      <x:c r="G264" s="29"/>
     </x:row>
     <x:row r="265">
       <x:c r="A265" s="21"/>
       <x:c r="B265" s="22"/>
       <x:c r="C265" s="14"/>
-      <x:c r="D265" s="27"/>
-      <x:c r="E265" s="27"/>
-      <x:c r="F265" s="28"/>
+      <x:c r="D265" s="26"/>
+      <x:c r="E265" s="14"/>
+      <x:c r="F265" s="26"/>
+      <x:c r="G265" s="29"/>
     </x:row>
     <x:row r="266">
       <x:c r="A266" s="21"/>
       <x:c r="B266" s="22"/>
       <x:c r="C266" s="14"/>
-      <x:c r="D266" s="27"/>
-      <x:c r="E266" s="27"/>
-      <x:c r="F266" s="28"/>
+      <x:c r="D266" s="26"/>
+      <x:c r="E266" s="14"/>
+      <x:c r="F266" s="26"/>
+      <x:c r="G266" s="29"/>
     </x:row>
     <x:row r="267">
       <x:c r="A267" s="21"/>
       <x:c r="B267" s="22"/>
       <x:c r="C267" s="14"/>
-      <x:c r="D267" s="27"/>
-      <x:c r="E267" s="27"/>
-      <x:c r="F267" s="28"/>
+      <x:c r="D267" s="26"/>
+      <x:c r="E267" s="14"/>
+      <x:c r="F267" s="26"/>
+      <x:c r="G267" s="29"/>
     </x:row>
     <x:row r="268">
       <x:c r="A268" s="21"/>
       <x:c r="B268" s="22"/>
       <x:c r="C268" s="14"/>
-      <x:c r="D268" s="27"/>
-      <x:c r="E268" s="27"/>
-      <x:c r="F268" s="28"/>
+      <x:c r="D268" s="26"/>
+      <x:c r="E268" s="14"/>
+      <x:c r="F268" s="26"/>
+      <x:c r="G268" s="29"/>
     </x:row>
     <x:row r="269">
       <x:c r="A269" s="21"/>
       <x:c r="B269" s="22"/>
       <x:c r="C269" s="14"/>
-      <x:c r="D269" s="27"/>
-      <x:c r="E269" s="27"/>
-      <x:c r="F269" s="28"/>
+      <x:c r="D269" s="26"/>
+      <x:c r="E269" s="14"/>
+      <x:c r="F269" s="26"/>
+      <x:c r="G269" s="29"/>
     </x:row>
     <x:row r="270">
       <x:c r="A270" s="21"/>
       <x:c r="B270" s="22"/>
       <x:c r="C270" s="14"/>
-      <x:c r="D270" s="27"/>
-      <x:c r="E270" s="27"/>
-      <x:c r="F270" s="28"/>
+      <x:c r="D270" s="26"/>
+      <x:c r="E270" s="14"/>
+      <x:c r="F270" s="26"/>
+      <x:c r="G270" s="29"/>
     </x:row>
     <x:row r="271">
       <x:c r="A271" s="21"/>
       <x:c r="B271" s="22"/>
       <x:c r="C271" s="14"/>
-      <x:c r="D271" s="27"/>
-      <x:c r="E271" s="27"/>
-      <x:c r="F271" s="28"/>
+      <x:c r="D271" s="26"/>
+      <x:c r="E271" s="14"/>
+      <x:c r="F271" s="26"/>
+      <x:c r="G271" s="29"/>
     </x:row>
     <x:row r="272">
       <x:c r="A272" s="21"/>
       <x:c r="B272" s="22"/>
       <x:c r="C272" s="14"/>
-      <x:c r="D272" s="27"/>
-      <x:c r="E272" s="27"/>
-      <x:c r="F272" s="28"/>
+      <x:c r="D272" s="26"/>
+      <x:c r="E272" s="14"/>
+      <x:c r="F272" s="26"/>
+      <x:c r="G272" s="29"/>
     </x:row>
     <x:row r="273">
       <x:c r="A273" s="21"/>
       <x:c r="B273" s="22"/>
       <x:c r="C273" s="14"/>
-      <x:c r="D273" s="27"/>
-      <x:c r="E273" s="27"/>
-      <x:c r="F273" s="28"/>
+      <x:c r="D273" s="26"/>
+      <x:c r="E273" s="14"/>
+      <x:c r="F273" s="26"/>
+      <x:c r="G273" s="29"/>
     </x:row>
     <x:row r="274">
       <x:c r="A274" s="21"/>
       <x:c r="B274" s="22"/>
       <x:c r="C274" s="14"/>
-      <x:c r="D274" s="27"/>
-      <x:c r="E274" s="27"/>
-      <x:c r="F274" s="28"/>
+      <x:c r="D274" s="26"/>
+      <x:c r="E274" s="14"/>
+      <x:c r="F274" s="26"/>
+      <x:c r="G274" s="29"/>
     </x:row>
     <x:row r="275">
       <x:c r="A275" s="21"/>
       <x:c r="B275" s="22"/>
       <x:c r="C275" s="14"/>
-      <x:c r="D275" s="27"/>
-      <x:c r="E275" s="27"/>
-      <x:c r="F275" s="28"/>
+      <x:c r="D275" s="26"/>
+      <x:c r="E275" s="14"/>
+      <x:c r="F275" s="26"/>
+      <x:c r="G275" s="29"/>
     </x:row>
     <x:row r="276">
       <x:c r="A276" s="21"/>
       <x:c r="B276" s="22"/>
       <x:c r="C276" s="14"/>
-      <x:c r="D276" s="27"/>
-      <x:c r="E276" s="27"/>
-      <x:c r="F276" s="28"/>
+      <x:c r="D276" s="26"/>
+      <x:c r="E276" s="14"/>
+      <x:c r="F276" s="26"/>
+      <x:c r="G276" s="29"/>
     </x:row>
     <x:row r="277">
       <x:c r="A277" s="21"/>
       <x:c r="B277" s="22"/>
       <x:c r="C277" s="14"/>
-      <x:c r="D277" s="27"/>
-      <x:c r="E277" s="27"/>
-      <x:c r="F277" s="28"/>
+      <x:c r="D277" s="26"/>
+      <x:c r="E277" s="14"/>
+      <x:c r="F277" s="26"/>
+      <x:c r="G277" s="29"/>
     </x:row>
     <x:row r="278">
       <x:c r="A278" s="21"/>
       <x:c r="B278" s="22"/>
       <x:c r="C278" s="14"/>
-      <x:c r="D278" s="27"/>
-      <x:c r="E278" s="27"/>
-      <x:c r="F278" s="28"/>
+      <x:c r="D278" s="26"/>
+      <x:c r="E278" s="14"/>
+      <x:c r="F278" s="26"/>
+      <x:c r="G278" s="29"/>
     </x:row>
     <x:row r="279">
       <x:c r="A279" s="21"/>
       <x:c r="B279" s="22"/>
       <x:c r="C279" s="14"/>
-      <x:c r="D279" s="27"/>
-      <x:c r="E279" s="27"/>
-      <x:c r="F279" s="28"/>
+      <x:c r="D279" s="26"/>
+      <x:c r="E279" s="14"/>
+      <x:c r="F279" s="26"/>
+      <x:c r="G279" s="29"/>
     </x:row>
     <x:row r="280">
       <x:c r="A280" s="21"/>
       <x:c r="B280" s="22"/>
       <x:c r="C280" s="14"/>
-      <x:c r="D280" s="27"/>
-      <x:c r="E280" s="27"/>
-      <x:c r="F280" s="28"/>
+      <x:c r="D280" s="26"/>
+      <x:c r="E280" s="14"/>
+      <x:c r="F280" s="26"/>
+      <x:c r="G280" s="29"/>
     </x:row>
     <x:row r="281">
       <x:c r="A281" s="21"/>
       <x:c r="B281" s="22"/>
       <x:c r="C281" s="14"/>
-      <x:c r="D281" s="27"/>
-      <x:c r="E281" s="27"/>
-      <x:c r="F281" s="28"/>
+      <x:c r="D281" s="26"/>
+      <x:c r="E281" s="14"/>
+      <x:c r="F281" s="26"/>
+      <x:c r="G281" s="29"/>
     </x:row>
     <x:row r="282">
       <x:c r="A282" s="21"/>
       <x:c r="B282" s="22"/>
       <x:c r="C282" s="14"/>
-      <x:c r="D282" s="27"/>
-      <x:c r="E282" s="27"/>
-      <x:c r="F282" s="28"/>
+      <x:c r="D282" s="26"/>
+      <x:c r="E282" s="14"/>
+      <x:c r="F282" s="26"/>
+      <x:c r="G282" s="29"/>
     </x:row>
     <x:row r="283">
       <x:c r="A283" s="21"/>
       <x:c r="B283" s="22"/>
       <x:c r="C283" s="14"/>
-      <x:c r="D283" s="27"/>
-      <x:c r="E283" s="27"/>
-      <x:c r="F283" s="28"/>
+      <x:c r="D283" s="26"/>
+      <x:c r="E283" s="14"/>
+      <x:c r="F283" s="26"/>
+      <x:c r="G283" s="29"/>
     </x:row>
     <x:row r="284">
       <x:c r="A284" s="21"/>
       <x:c r="B284" s="22"/>
       <x:c r="C284" s="14"/>
-      <x:c r="D284" s="27"/>
-      <x:c r="E284" s="27"/>
-      <x:c r="F284" s="28"/>
+      <x:c r="D284" s="26"/>
+      <x:c r="E284" s="14"/>
+      <x:c r="F284" s="26"/>
+      <x:c r="G284" s="29"/>
     </x:row>
     <x:row r="285">
       <x:c r="A285" s="21"/>
       <x:c r="B285" s="22"/>
       <x:c r="C285" s="14"/>
-      <x:c r="D285" s="27"/>
-      <x:c r="E285" s="27"/>
-      <x:c r="F285" s="28"/>
+      <x:c r="D285" s="26"/>
+      <x:c r="E285" s="14"/>
+      <x:c r="F285" s="26"/>
+      <x:c r="G285" s="29"/>
     </x:row>
     <x:row r="286">
       <x:c r="A286" s="21"/>
       <x:c r="B286" s="22"/>
       <x:c r="C286" s="14"/>
-      <x:c r="D286" s="27"/>
-      <x:c r="E286" s="27"/>
-      <x:c r="F286" s="28"/>
+      <x:c r="D286" s="26"/>
+      <x:c r="E286" s="14"/>
+      <x:c r="F286" s="26"/>
+      <x:c r="G286" s="29"/>
     </x:row>
     <x:row r="287">
       <x:c r="A287" s="21"/>
       <x:c r="B287" s="22"/>
       <x:c r="C287" s="14"/>
-      <x:c r="D287" s="27"/>
-      <x:c r="E287" s="27"/>
-      <x:c r="F287" s="28"/>
+      <x:c r="D287" s="26"/>
+      <x:c r="E287" s="14"/>
+      <x:c r="F287" s="26"/>
+      <x:c r="G287" s="29"/>
     </x:row>
     <x:row r="288">
       <x:c r="A288" s="21"/>
       <x:c r="B288" s="22"/>
       <x:c r="C288" s="14"/>
-      <x:c r="D288" s="27"/>
-      <x:c r="E288" s="27"/>
-      <x:c r="F288" s="28"/>
+      <x:c r="D288" s="26"/>
+      <x:c r="E288" s="14"/>
+      <x:c r="F288" s="26"/>
+      <x:c r="G288" s="29"/>
     </x:row>
     <x:row r="289">
       <x:c r="A289" s="21"/>
       <x:c r="B289" s="22"/>
       <x:c r="C289" s="14"/>
-      <x:c r="D289" s="27"/>
-      <x:c r="E289" s="27"/>
-      <x:c r="F289" s="28"/>
+      <x:c r="D289" s="26"/>
+      <x:c r="E289" s="14"/>
+      <x:c r="F289" s="26"/>
+      <x:c r="G289" s="29"/>
     </x:row>
     <x:row r="290">
       <x:c r="A290" s="21"/>
       <x:c r="B290" s="22"/>
       <x:c r="C290" s="14"/>
-      <x:c r="D290" s="27"/>
-      <x:c r="E290" s="27"/>
-      <x:c r="F290" s="28"/>
+      <x:c r="D290" s="26"/>
+      <x:c r="E290" s="14"/>
+      <x:c r="F290" s="26"/>
+      <x:c r="G290" s="29"/>
     </x:row>
     <x:row r="291">
       <x:c r="A291" s="21"/>
       <x:c r="B291" s="22"/>
       <x:c r="C291" s="14"/>
-      <x:c r="D291" s="27"/>
-      <x:c r="E291" s="27"/>
-      <x:c r="F291" s="28"/>
+      <x:c r="D291" s="26"/>
+      <x:c r="E291" s="14"/>
+      <x:c r="F291" s="26"/>
+      <x:c r="G291" s="29"/>
     </x:row>
     <x:row r="292">
       <x:c r="A292" s="21"/>
       <x:c r="B292" s="22"/>
       <x:c r="C292" s="14"/>
-      <x:c r="D292" s="27"/>
-      <x:c r="E292" s="27"/>
-      <x:c r="F292" s="28"/>
+      <x:c r="D292" s="26"/>
+      <x:c r="E292" s="14"/>
+      <x:c r="F292" s="26"/>
+      <x:c r="G292" s="29"/>
     </x:row>
     <x:row r="293">
       <x:c r="A293" s="21"/>
       <x:c r="B293" s="22"/>
       <x:c r="C293" s="14"/>
-      <x:c r="D293" s="27"/>
-      <x:c r="E293" s="27"/>
-      <x:c r="F293" s="28"/>
+      <x:c r="D293" s="26"/>
+      <x:c r="E293" s="14"/>
+      <x:c r="F293" s="26"/>
+      <x:c r="G293" s="29"/>
     </x:row>
     <x:row r="294">
       <x:c r="A294" s="21"/>
       <x:c r="B294" s="22"/>
       <x:c r="C294" s="14"/>
-      <x:c r="D294" s="27"/>
-      <x:c r="E294" s="27"/>
-      <x:c r="F294" s="28"/>
+      <x:c r="D294" s="26"/>
+      <x:c r="E294" s="14"/>
+      <x:c r="F294" s="26"/>
+      <x:c r="G294" s="29"/>
     </x:row>
     <x:row r="295">
       <x:c r="A295" s="21"/>
       <x:c r="B295" s="22"/>
       <x:c r="C295" s="14"/>
-      <x:c r="D295" s="27"/>
-      <x:c r="E295" s="27"/>
-      <x:c r="F295" s="28"/>
+      <x:c r="D295" s="26"/>
+      <x:c r="E295" s="14"/>
+      <x:c r="F295" s="26"/>
+      <x:c r="G295" s="29"/>
     </x:row>
     <x:row r="296">
       <x:c r="A296" s="21"/>
       <x:c r="B296" s="22"/>
       <x:c r="C296" s="14"/>
-      <x:c r="D296" s="27"/>
-      <x:c r="E296" s="27"/>
-      <x:c r="F296" s="28"/>
+      <x:c r="D296" s="26"/>
+      <x:c r="E296" s="14"/>
+      <x:c r="F296" s="26"/>
+      <x:c r="G296" s="29"/>
     </x:row>
     <x:row r="297">
       <x:c r="A297" s="21"/>
       <x:c r="B297" s="22"/>
       <x:c r="C297" s="14"/>
-      <x:c r="D297" s="27"/>
-      <x:c r="E297" s="27"/>
-      <x:c r="F297" s="28"/>
+      <x:c r="D297" s="26"/>
+      <x:c r="E297" s="14"/>
+      <x:c r="F297" s="26"/>
+      <x:c r="G297" s="29"/>
     </x:row>
     <x:row r="298">
       <x:c r="A298" s="21"/>
       <x:c r="B298" s="22"/>
       <x:c r="C298" s="14"/>
-      <x:c r="D298" s="27"/>
-      <x:c r="E298" s="27"/>
-      <x:c r="F298" s="28"/>
+      <x:c r="D298" s="26"/>
+      <x:c r="E298" s="14"/>
+      <x:c r="F298" s="26"/>
+      <x:c r="G298" s="29"/>
     </x:row>
     <x:row r="299">
       <x:c r="A299" s="21"/>
       <x:c r="B299" s="22"/>
       <x:c r="C299" s="14"/>
-      <x:c r="D299" s="27"/>
-      <x:c r="E299" s="27"/>
-      <x:c r="F299" s="28"/>
+      <x:c r="D299" s="26"/>
+      <x:c r="E299" s="14"/>
+      <x:c r="F299" s="26"/>
+      <x:c r="G299" s="29"/>
     </x:row>
     <x:row r="300">
       <x:c r="A300" s="21"/>
       <x:c r="B300" s="22"/>
       <x:c r="C300" s="14"/>
-      <x:c r="D300" s="27"/>
-      <x:c r="E300" s="27"/>
-      <x:c r="F300" s="28"/>
+      <x:c r="D300" s="26"/>
+      <x:c r="E300" s="14"/>
+      <x:c r="F300" s="26"/>
+      <x:c r="G300" s="29"/>
     </x:row>
     <x:row r="301">
       <x:c r="A301" s="21"/>
       <x:c r="B301" s="22"/>
       <x:c r="C301" s="14"/>
-      <x:c r="D301" s="27"/>
-      <x:c r="E301" s="27"/>
-      <x:c r="F301" s="28"/>
+      <x:c r="D301" s="26"/>
+      <x:c r="E301" s="14"/>
+      <x:c r="F301" s="26"/>
+      <x:c r="G301" s="29"/>
     </x:row>
     <x:row r="302">
       <x:c r="A302" s="21"/>
       <x:c r="B302" s="22"/>
       <x:c r="C302" s="14"/>
-      <x:c r="D302" s="27"/>
-      <x:c r="E302" s="27"/>
-      <x:c r="F302" s="28"/>
+      <x:c r="D302" s="26"/>
+      <x:c r="E302" s="14"/>
+      <x:c r="F302" s="26"/>
+      <x:c r="G302" s="29"/>
     </x:row>
     <x:row r="303">
       <x:c r="A303" s="21"/>
       <x:c r="B303" s="22"/>
       <x:c r="C303" s="14"/>
-      <x:c r="D303" s="27"/>
-      <x:c r="E303" s="27"/>
-      <x:c r="F303" s="28"/>
+      <x:c r="D303" s="26"/>
+      <x:c r="E303" s="14"/>
+      <x:c r="F303" s="26"/>
+      <x:c r="G303" s="29"/>
     </x:row>
     <x:row r="304">
       <x:c r="A304" s="21"/>
       <x:c r="B304" s="22"/>
       <x:c r="C304" s="14"/>
-      <x:c r="D304" s="27"/>
-      <x:c r="E304" s="27"/>
-      <x:c r="F304" s="28"/>
+      <x:c r="D304" s="26"/>
+      <x:c r="E304" s="14"/>
+      <x:c r="F304" s="26"/>
+      <x:c r="G304" s="29"/>
     </x:row>
     <x:row r="305">
       <x:c r="A305" s="21"/>
       <x:c r="B305" s="22"/>
       <x:c r="C305" s="14"/>
-      <x:c r="D305" s="27"/>
-      <x:c r="E305" s="27"/>
-      <x:c r="F305" s="28"/>
+      <x:c r="D305" s="26"/>
+      <x:c r="E305" s="14"/>
+      <x:c r="F305" s="26"/>
+      <x:c r="G305" s="29"/>
     </x:row>
     <x:row r="306">
       <x:c r="A306" s="21"/>
       <x:c r="B306" s="22"/>
       <x:c r="C306" s="14"/>
-      <x:c r="D306" s="27"/>
-      <x:c r="E306" s="27"/>
-      <x:c r="F306" s="28"/>
+      <x:c r="D306" s="26"/>
+      <x:c r="E306" s="14"/>
+      <x:c r="F306" s="26"/>
+      <x:c r="G306" s="29"/>
     </x:row>
     <x:row r="307">
       <x:c r="A307" s="21"/>
       <x:c r="B307" s="22"/>
       <x:c r="C307" s="14"/>
-      <x:c r="D307" s="27"/>
-      <x:c r="E307" s="27"/>
-      <x:c r="F307" s="28"/>
+      <x:c r="D307" s="26"/>
+      <x:c r="E307" s="14"/>
+      <x:c r="F307" s="26"/>
+      <x:c r="G307" s="29"/>
     </x:row>
     <x:row r="308">
       <x:c r="A308" s="21"/>
       <x:c r="B308" s="22"/>
       <x:c r="C308" s="14"/>
-      <x:c r="D308" s="27"/>
-      <x:c r="E308" s="27"/>
-      <x:c r="F308" s="28"/>
+      <x:c r="D308" s="26"/>
+      <x:c r="E308" s="14"/>
+      <x:c r="F308" s="26"/>
+      <x:c r="G308" s="29"/>
     </x:row>
     <x:row r="309">
       <x:c r="A309" s="21"/>
       <x:c r="B309" s="22"/>
       <x:c r="C309" s="14"/>
-      <x:c r="D309" s="27"/>
-      <x:c r="E309" s="27"/>
-      <x:c r="F309" s="28"/>
+      <x:c r="D309" s="26"/>
+      <x:c r="E309" s="14"/>
+      <x:c r="F309" s="26"/>
+      <x:c r="G309" s="29"/>
     </x:row>
     <x:row r="310">
       <x:c r="A310" s="21"/>
       <x:c r="B310" s="22"/>
       <x:c r="C310" s="14"/>
-      <x:c r="D310" s="27"/>
-      <x:c r="E310" s="27"/>
-      <x:c r="F310" s="28"/>
+      <x:c r="D310" s="26"/>
+      <x:c r="E310" s="14"/>
+      <x:c r="F310" s="26"/>
+      <x:c r="G310" s="29"/>
     </x:row>
     <x:row r="311">
       <x:c r="A311" s="21"/>
       <x:c r="B311" s="22"/>
       <x:c r="C311" s="14"/>
-      <x:c r="D311" s="27"/>
-      <x:c r="E311" s="27"/>
-      <x:c r="F311" s="28"/>
+      <x:c r="D311" s="26"/>
+      <x:c r="E311" s="14"/>
+      <x:c r="F311" s="26"/>
+      <x:c r="G311" s="29"/>
     </x:row>
     <x:row r="312">
       <x:c r="A312" s="21"/>
       <x:c r="B312" s="22"/>
       <x:c r="C312" s="14"/>
-      <x:c r="D312" s="27"/>
-      <x:c r="E312" s="27"/>
-      <x:c r="F312" s="28"/>
+      <x:c r="D312" s="26"/>
+      <x:c r="E312" s="14"/>
+      <x:c r="F312" s="26"/>
+      <x:c r="G312" s="29"/>
     </x:row>
     <x:row r="313">
       <x:c r="A313" s="21"/>
       <x:c r="B313" s="22"/>
       <x:c r="C313" s="14"/>
-      <x:c r="D313" s="27"/>
-      <x:c r="E313" s="27"/>
-      <x:c r="F313" s="28"/>
+      <x:c r="D313" s="26"/>
+      <x:c r="E313" s="14"/>
+      <x:c r="F313" s="26"/>
+      <x:c r="G313" s="29"/>
     </x:row>
     <x:row r="314">
       <x:c r="A314" s="21"/>
       <x:c r="B314" s="22"/>
       <x:c r="C314" s="14"/>
-      <x:c r="D314" s="27"/>
-      <x:c r="E314" s="27"/>
-      <x:c r="F314" s="28"/>
+      <x:c r="D314" s="26"/>
+      <x:c r="E314" s="14"/>
+      <x:c r="F314" s="26"/>
+      <x:c r="G314" s="29"/>
     </x:row>
     <x:row r="315">
       <x:c r="A315" s="21"/>
       <x:c r="B315" s="22"/>
       <x:c r="C315" s="14"/>
-      <x:c r="D315" s="27"/>
-      <x:c r="E315" s="27"/>
-      <x:c r="F315" s="28"/>
+      <x:c r="D315" s="26"/>
+      <x:c r="E315" s="14"/>
+      <x:c r="F315" s="26"/>
+      <x:c r="G315" s="29"/>
     </x:row>
     <x:row r="316">
       <x:c r="A316" s="21"/>
       <x:c r="B316" s="22"/>
       <x:c r="C316" s="14"/>
-      <x:c r="D316" s="27"/>
-      <x:c r="E316" s="27"/>
-      <x:c r="F316" s="28"/>
+      <x:c r="D316" s="26"/>
+      <x:c r="E316" s="14"/>
+      <x:c r="F316" s="26"/>
+      <x:c r="G316" s="29"/>
     </x:row>
     <x:row r="317">
       <x:c r="A317" s="21"/>
       <x:c r="B317" s="22"/>
       <x:c r="C317" s="14"/>
-      <x:c r="D317" s="27"/>
-      <x:c r="E317" s="27"/>
-      <x:c r="F317" s="28"/>
+      <x:c r="D317" s="26"/>
+      <x:c r="E317" s="14"/>
+      <x:c r="F317" s="26"/>
+      <x:c r="G317" s="29"/>
     </x:row>
     <x:row r="318">
       <x:c r="A318" s="21"/>
       <x:c r="B318" s="22"/>
       <x:c r="C318" s="14"/>
-      <x:c r="D318" s="27"/>
-      <x:c r="E318" s="27"/>
-      <x:c r="F318" s="28"/>
+      <x:c r="D318" s="26"/>
+      <x:c r="E318" s="14"/>
+      <x:c r="F318" s="26"/>
+      <x:c r="G318" s="29"/>
     </x:row>
     <x:row r="319">
       <x:c r="A319" s="21"/>
       <x:c r="B319" s="22"/>
       <x:c r="C319" s="14"/>
-      <x:c r="D319" s="27"/>
-      <x:c r="E319" s="27"/>
-      <x:c r="F319" s="28"/>
+      <x:c r="D319" s="26"/>
+      <x:c r="E319" s="14"/>
+      <x:c r="F319" s="26"/>
+      <x:c r="G319" s="29"/>
     </x:row>
     <x:row r="320">
       <x:c r="A320" s="21"/>
       <x:c r="B320" s="22"/>
       <x:c r="C320" s="14"/>
-      <x:c r="D320" s="27"/>
-      <x:c r="E320" s="27"/>
-      <x:c r="F320" s="28"/>
+      <x:c r="D320" s="26"/>
+      <x:c r="E320" s="14"/>
+      <x:c r="F320" s="26"/>
+      <x:c r="G320" s="29"/>
     </x:row>
     <x:row r="321">
       <x:c r="A321" s="21"/>
       <x:c r="B321" s="22"/>
       <x:c r="C321" s="14"/>
-      <x:c r="D321" s="27"/>
-      <x:c r="E321" s="27"/>
-      <x:c r="F321" s="28"/>
+      <x:c r="D321" s="26"/>
+      <x:c r="E321" s="14"/>
+      <x:c r="F321" s="26"/>
+      <x:c r="G321" s="29"/>
     </x:row>
     <x:row r="322">
       <x:c r="A322" s="21"/>
       <x:c r="B322" s="22"/>
       <x:c r="C322" s="14"/>
-      <x:c r="D322" s="27"/>
-      <x:c r="E322" s="27"/>
-      <x:c r="F322" s="28"/>
+      <x:c r="D322" s="26"/>
+      <x:c r="E322" s="14"/>
+      <x:c r="F322" s="26"/>
+      <x:c r="G322" s="29"/>
     </x:row>
     <x:row r="323">
       <x:c r="A323" s="21"/>
       <x:c r="B323" s="22"/>
       <x:c r="C323" s="14"/>
-      <x:c r="D323" s="27"/>
-      <x:c r="E323" s="27"/>
-      <x:c r="F323" s="28"/>
+      <x:c r="D323" s="26"/>
+      <x:c r="E323" s="14"/>
+      <x:c r="F323" s="26"/>
+      <x:c r="G323" s="29"/>
     </x:row>
     <x:row r="324">
       <x:c r="A324" s="21"/>
       <x:c r="B324" s="22"/>
       <x:c r="C324" s="14"/>
-      <x:c r="D324" s="27"/>
-      <x:c r="E324" s="27"/>
-      <x:c r="F324" s="28"/>
+      <x:c r="D324" s="26"/>
+      <x:c r="E324" s="14"/>
+      <x:c r="F324" s="26"/>
+      <x:c r="G324" s="29"/>
     </x:row>
     <x:row r="325">
       <x:c r="A325" s="21"/>
       <x:c r="B325" s="22"/>
       <x:c r="C325" s="14"/>
-      <x:c r="D325" s="27"/>
-      <x:c r="E325" s="27"/>
-      <x:c r="F325" s="28"/>
+      <x:c r="D325" s="26"/>
+      <x:c r="E325" s="14"/>
+      <x:c r="F325" s="26"/>
+      <x:c r="G325" s="29"/>
     </x:row>
     <x:row r="326">
       <x:c r="A326" s="21"/>
       <x:c r="B326" s="22"/>
       <x:c r="C326" s="14"/>
-      <x:c r="D326" s="27"/>
-      <x:c r="E326" s="27"/>
-      <x:c r="F326" s="28"/>
+      <x:c r="D326" s="26"/>
+      <x:c r="E326" s="14"/>
+      <x:c r="F326" s="26"/>
+      <x:c r="G326" s="29"/>
     </x:row>
     <x:row r="327">
       <x:c r="A327" s="21"/>
       <x:c r="B327" s="22"/>
       <x:c r="C327" s="14"/>
-      <x:c r="D327" s="27"/>
-      <x:c r="E327" s="27"/>
-      <x:c r="F327" s="28"/>
+      <x:c r="D327" s="26"/>
+      <x:c r="E327" s="14"/>
+      <x:c r="F327" s="26"/>
+      <x:c r="G327" s="29"/>
     </x:row>
     <x:row r="328">
       <x:c r="A328" s="21"/>
       <x:c r="B328" s="22"/>
       <x:c r="C328" s="14"/>
-      <x:c r="D328" s="27"/>
-      <x:c r="E328" s="27"/>
-      <x:c r="F328" s="28"/>
+      <x:c r="D328" s="26"/>
+      <x:c r="E328" s="14"/>
+      <x:c r="F328" s="26"/>
+      <x:c r="G328" s="29"/>
     </x:row>
     <x:row r="329">
       <x:c r="A329" s="21"/>
       <x:c r="B329" s="22"/>
       <x:c r="C329" s="14"/>
-      <x:c r="D329" s="27"/>
-      <x:c r="E329" s="27"/>
-      <x:c r="F329" s="28"/>
+      <x:c r="D329" s="26"/>
+      <x:c r="E329" s="14"/>
+      <x:c r="F329" s="26"/>
+      <x:c r="G329" s="29"/>
     </x:row>
     <x:row r="330">
       <x:c r="A330" s="21"/>
       <x:c r="B330" s="22"/>
       <x:c r="C330" s="14"/>
-      <x:c r="D330" s="27"/>
-      <x:c r="E330" s="27"/>
-      <x:c r="F330" s="28"/>
+      <x:c r="D330" s="26"/>
+      <x:c r="E330" s="14"/>
+      <x:c r="F330" s="26"/>
+      <x:c r="G330" s="29"/>
     </x:row>
     <x:row r="331">
       <x:c r="A331" s="21"/>
       <x:c r="B331" s="22"/>
       <x:c r="C331" s="14"/>
-      <x:c r="D331" s="27"/>
-      <x:c r="E331" s="27"/>
-      <x:c r="F331" s="28"/>
+      <x:c r="D331" s="26"/>
+      <x:c r="E331" s="14"/>
+      <x:c r="F331" s="26"/>
+      <x:c r="G331" s="29"/>
     </x:row>
     <x:row r="332">
       <x:c r="A332" s="21"/>
       <x:c r="B332" s="22"/>
       <x:c r="C332" s="14"/>
-      <x:c r="D332" s="27"/>
-      <x:c r="E332" s="27"/>
-      <x:c r="F332" s="28"/>
+      <x:c r="D332" s="26"/>
+      <x:c r="E332" s="14"/>
+      <x:c r="F332" s="26"/>
+      <x:c r="G332" s="29"/>
     </x:row>
     <x:row r="333">
       <x:c r="A333" s="21"/>
       <x:c r="B333" s="22"/>
       <x:c r="C333" s="14"/>
-      <x:c r="D333" s="27"/>
-      <x:c r="E333" s="27"/>
-      <x:c r="F333" s="28"/>
+      <x:c r="D333" s="26"/>
+      <x:c r="E333" s="14"/>
+      <x:c r="F333" s="26"/>
+      <x:c r="G333" s="29"/>
     </x:row>
     <x:row r="334">
       <x:c r="A334" s="21"/>
       <x:c r="B334" s="22"/>
       <x:c r="C334" s="14"/>
-      <x:c r="D334" s="27"/>
-      <x:c r="E334" s="27"/>
-      <x:c r="F334" s="28"/>
+      <x:c r="D334" s="26"/>
+      <x:c r="E334" s="14"/>
+      <x:c r="F334" s="26"/>
+      <x:c r="G334" s="29"/>
     </x:row>
     <x:row r="335">
       <x:c r="A335" s="21"/>
       <x:c r="B335" s="22"/>
       <x:c r="C335" s="14"/>
-      <x:c r="D335" s="27"/>
-      <x:c r="E335" s="27"/>
-      <x:c r="F335" s="28"/>
+      <x:c r="D335" s="26"/>
+      <x:c r="E335" s="14"/>
+      <x:c r="F335" s="26"/>
+      <x:c r="G335" s="29"/>
     </x:row>
     <x:row r="336">
       <x:c r="A336" s="21"/>
       <x:c r="B336" s="22"/>
       <x:c r="C336" s="14"/>
-      <x:c r="D336" s="27"/>
-      <x:c r="E336" s="27"/>
-      <x:c r="F336" s="28"/>
+      <x:c r="D336" s="26"/>
+      <x:c r="E336" s="14"/>
+      <x:c r="F336" s="26"/>
+      <x:c r="G336" s="29"/>
     </x:row>
     <x:row r="337">
       <x:c r="A337" s="21"/>
       <x:c r="B337" s="22"/>
       <x:c r="C337" s="14"/>
-      <x:c r="D337" s="27"/>
-      <x:c r="E337" s="27"/>
-      <x:c r="F337" s="28"/>
+      <x:c r="D337" s="26"/>
+      <x:c r="E337" s="14"/>
+      <x:c r="F337" s="26"/>
+      <x:c r="G337" s="29"/>
     </x:row>
     <x:row r="338">
       <x:c r="A338" s="21"/>
       <x:c r="B338" s="22"/>
       <x:c r="C338" s="14"/>
-      <x:c r="D338" s="27"/>
-      <x:c r="E338" s="27"/>
-      <x:c r="F338" s="28"/>
+      <x:c r="D338" s="26"/>
+      <x:c r="E338" s="14"/>
+      <x:c r="F338" s="26"/>
+      <x:c r="G338" s="29"/>
     </x:row>
     <x:row r="339">
       <x:c r="A339" s="21"/>
       <x:c r="B339" s="22"/>
       <x:c r="C339" s="14"/>
-      <x:c r="D339" s="27"/>
-      <x:c r="E339" s="27"/>
-      <x:c r="F339" s="28"/>
+      <x:c r="D339" s="26"/>
+      <x:c r="E339" s="14"/>
+      <x:c r="F339" s="26"/>
+      <x:c r="G339" s="29"/>
     </x:row>
     <x:row r="340">
       <x:c r="A340" s="21"/>
       <x:c r="B340" s="22"/>
       <x:c r="C340" s="14"/>
-      <x:c r="D340" s="27"/>
-      <x:c r="E340" s="27"/>
-      <x:c r="F340" s="28"/>
+      <x:c r="D340" s="26"/>
+      <x:c r="E340" s="14"/>
+      <x:c r="F340" s="26"/>
+      <x:c r="G340" s="29"/>
     </x:row>
     <x:row r="341">
       <x:c r="A341" s="21"/>
       <x:c r="B341" s="22"/>
       <x:c r="C341" s="14"/>
-      <x:c r="D341" s="27"/>
-      <x:c r="E341" s="27"/>
-      <x:c r="F341" s="28"/>
+      <x:c r="D341" s="26"/>
+      <x:c r="E341" s="14"/>
+      <x:c r="F341" s="26"/>
+      <x:c r="G341" s="29"/>
     </x:row>
     <x:row r="342">
       <x:c r="A342" s="21"/>
       <x:c r="B342" s="22"/>
       <x:c r="C342" s="14"/>
-      <x:c r="D342" s="27"/>
-      <x:c r="E342" s="27"/>
-      <x:c r="F342" s="28"/>
+      <x:c r="D342" s="26"/>
+      <x:c r="E342" s="14"/>
+      <x:c r="F342" s="26"/>
+      <x:c r="G342" s="29"/>
     </x:row>
     <x:row r="343">
       <x:c r="A343" s="21"/>
       <x:c r="B343" s="22"/>
       <x:c r="C343" s="14"/>
-      <x:c r="D343" s="27"/>
-      <x:c r="E343" s="27"/>
-      <x:c r="F343" s="28"/>
+      <x:c r="D343" s="26"/>
+      <x:c r="E343" s="14"/>
+      <x:c r="F343" s="26"/>
+      <x:c r="G343" s="29"/>
     </x:row>
     <x:row r="344">
       <x:c r="A344" s="21"/>
       <x:c r="B344" s="22"/>
       <x:c r="C344" s="14"/>
-      <x:c r="D344" s="27"/>
-      <x:c r="E344" s="27"/>
-      <x:c r="F344" s="28"/>
+      <x:c r="D344" s="26"/>
+      <x:c r="E344" s="14"/>
+      <x:c r="F344" s="26"/>
+      <x:c r="G344" s="29"/>
     </x:row>
     <x:row r="345">
       <x:c r="A345" s="21"/>
       <x:c r="B345" s="22"/>
       <x:c r="C345" s="14"/>
-      <x:c r="D345" s="27"/>
-      <x:c r="E345" s="27"/>
-      <x:c r="F345" s="28"/>
+      <x:c r="D345" s="26"/>
+      <x:c r="E345" s="14"/>
+      <x:c r="F345" s="26"/>
+      <x:c r="G345" s="29"/>
     </x:row>
     <x:row r="346">
       <x:c r="A346" s="21"/>
       <x:c r="B346" s="22"/>
       <x:c r="C346" s="14"/>
-      <x:c r="D346" s="27"/>
-      <x:c r="E346" s="27"/>
-      <x:c r="F346" s="28"/>
+      <x:c r="D346" s="26"/>
+      <x:c r="E346" s="14"/>
+      <x:c r="F346" s="26"/>
+      <x:c r="G346" s="29"/>
     </x:row>
     <x:row r="347">
       <x:c r="A347" s="21"/>
       <x:c r="B347" s="22"/>
       <x:c r="C347" s="14"/>
-      <x:c r="D347" s="27"/>
-      <x:c r="E347" s="27"/>
-      <x:c r="F347" s="28"/>
+      <x:c r="D347" s="26"/>
+      <x:c r="E347" s="14"/>
+      <x:c r="F347" s="26"/>
+      <x:c r="G347" s="29"/>
     </x:row>
     <x:row r="348">
       <x:c r="A348" s="21"/>
       <x:c r="B348" s="22"/>
       <x:c r="C348" s="14"/>
-      <x:c r="D348" s="27"/>
-      <x:c r="E348" s="27"/>
-      <x:c r="F348" s="28"/>
+      <x:c r="D348" s="26"/>
+      <x:c r="E348" s="14"/>
+      <x:c r="F348" s="26"/>
+      <x:c r="G348" s="29"/>
     </x:row>
     <x:row r="349">
       <x:c r="A349" s="21"/>
       <x:c r="B349" s="22"/>
       <x:c r="C349" s="14"/>
-      <x:c r="D349" s="27"/>
-      <x:c r="E349" s="27"/>
-      <x:c r="F349" s="28"/>
+      <x:c r="D349" s="26"/>
+      <x:c r="E349" s="14"/>
+      <x:c r="F349" s="26"/>
+      <x:c r="G349" s="29"/>
     </x:row>
     <x:row r="350">
       <x:c r="A350" s="21"/>
       <x:c r="B350" s="22"/>
       <x:c r="C350" s="14"/>
-      <x:c r="D350" s="27"/>
-      <x:c r="E350" s="27"/>
-      <x:c r="F350" s="28"/>
+      <x:c r="D350" s="26"/>
+      <x:c r="E350" s="14"/>
+      <x:c r="F350" s="26"/>
+      <x:c r="G350" s="29"/>
     </x:row>
     <x:row r="351">
       <x:c r="A351" s="21"/>
       <x:c r="B351" s="22"/>
       <x:c r="C351" s="14"/>
-      <x:c r="D351" s="27"/>
-      <x:c r="E351" s="27"/>
-      <x:c r="F351" s="28"/>
+      <x:c r="D351" s="26"/>
+      <x:c r="E351" s="14"/>
+      <x:c r="F351" s="26"/>
+      <x:c r="G351" s="29"/>
     </x:row>
     <x:row r="352">
       <x:c r="A352" s="21"/>
       <x:c r="B352" s="22"/>
       <x:c r="C352" s="14"/>
-      <x:c r="D352" s="27"/>
-      <x:c r="E352" s="27"/>
-      <x:c r="F352" s="28"/>
+      <x:c r="D352" s="26"/>
+      <x:c r="E352" s="14"/>
+      <x:c r="F352" s="26"/>
+      <x:c r="G352" s="29"/>
     </x:row>
     <x:row r="353">
       <x:c r="A353" s="21"/>
       <x:c r="B353" s="22"/>
       <x:c r="C353" s="14"/>
-      <x:c r="D353" s="27"/>
-      <x:c r="E353" s="27"/>
-      <x:c r="F353" s="28"/>
+      <x:c r="D353" s="26"/>
+      <x:c r="E353" s="14"/>
+      <x:c r="F353" s="26"/>
+      <x:c r="G353" s="29"/>
     </x:row>
     <x:row r="354">
       <x:c r="A354" s="21"/>
       <x:c r="B354" s="22"/>
       <x:c r="C354" s="14"/>
-      <x:c r="D354" s="27"/>
-      <x:c r="E354" s="27"/>
-      <x:c r="F354" s="28"/>
+      <x:c r="D354" s="26"/>
+      <x:c r="E354" s="14"/>
+      <x:c r="F354" s="26"/>
+      <x:c r="G354" s="29"/>
     </x:row>
     <x:row r="355">
       <x:c r="A355" s="21"/>
       <x:c r="B355" s="22"/>
       <x:c r="C355" s="14"/>
-      <x:c r="D355" s="27"/>
-      <x:c r="E355" s="27"/>
-      <x:c r="F355" s="28"/>
+      <x:c r="D355" s="26"/>
+      <x:c r="E355" s="14"/>
+      <x:c r="F355" s="26"/>
+      <x:c r="G355" s="29"/>
     </x:row>
     <x:row r="356">
       <x:c r="A356" s="21"/>
       <x:c r="B356" s="22"/>
       <x:c r="C356" s="14"/>
-      <x:c r="D356" s="27"/>
-      <x:c r="E356" s="27"/>
-      <x:c r="F356" s="28"/>
+      <x:c r="D356" s="26"/>
+      <x:c r="E356" s="14"/>
+      <x:c r="F356" s="26"/>
+      <x:c r="G356" s="29"/>
     </x:row>
     <x:row r="357">
       <x:c r="A357" s="21"/>
       <x:c r="B357" s="22"/>
       <x:c r="C357" s="14"/>
-      <x:c r="D357" s="27"/>
-      <x:c r="E357" s="27"/>
-      <x:c r="F357" s="28"/>
+      <x:c r="D357" s="26"/>
+      <x:c r="E357" s="14"/>
+      <x:c r="F357" s="26"/>
+      <x:c r="G357" s="29"/>
     </x:row>
     <x:row r="358">
       <x:c r="A358" s="21"/>
       <x:c r="B358" s="22"/>
       <x:c r="C358" s="14"/>
-      <x:c r="D358" s="27"/>
-      <x:c r="E358" s="27"/>
-      <x:c r="F358" s="28"/>
+      <x:c r="D358" s="26"/>
+      <x:c r="E358" s="14"/>
+      <x:c r="F358" s="26"/>
+      <x:c r="G358" s="29"/>
     </x:row>
     <x:row r="359">
       <x:c r="A359" s="21"/>
       <x:c r="B359" s="22"/>
       <x:c r="C359" s="14"/>
-      <x:c r="D359" s="27"/>
-      <x:c r="E359" s="27"/>
-      <x:c r="F359" s="28"/>
+      <x:c r="D359" s="26"/>
+      <x:c r="E359" s="14"/>
+      <x:c r="F359" s="26"/>
+      <x:c r="G359" s="29"/>
     </x:row>
     <x:row r="360">
       <x:c r="A360" s="21"/>
       <x:c r="B360" s="22"/>
       <x:c r="C360" s="14"/>
-      <x:c r="D360" s="27"/>
-      <x:c r="E360" s="27"/>
-      <x:c r="F360" s="28"/>
+      <x:c r="D360" s="26"/>
+      <x:c r="E360" s="14"/>
+      <x:c r="F360" s="26"/>
+      <x:c r="G360" s="29"/>
     </x:row>
     <x:row r="361">
       <x:c r="A361" s="21"/>
       <x:c r="B361" s="22"/>
       <x:c r="C361" s="14"/>
-      <x:c r="D361" s="27"/>
-      <x:c r="E361" s="27"/>
-      <x:c r="F361" s="28"/>
+      <x:c r="D361" s="26"/>
+      <x:c r="E361" s="14"/>
+      <x:c r="F361" s="26"/>
+      <x:c r="G361" s="29"/>
     </x:row>
     <x:row r="362">
       <x:c r="A362" s="21"/>
       <x:c r="B362" s="22"/>
       <x:c r="C362" s="14"/>
-      <x:c r="D362" s="27"/>
-      <x:c r="E362" s="27"/>
-      <x:c r="F362" s="28"/>
+      <x:c r="D362" s="26"/>
+      <x:c r="E362" s="14"/>
+      <x:c r="F362" s="26"/>
+      <x:c r="G362" s="29"/>
     </x:row>
     <x:row r="363">
       <x:c r="A363" s="21"/>
       <x:c r="B363" s="22"/>
       <x:c r="C363" s="14"/>
-      <x:c r="D363" s="27"/>
-      <x:c r="E363" s="27"/>
-      <x:c r="F363" s="28"/>
+      <x:c r="D363" s="26"/>
+      <x:c r="E363" s="14"/>
+      <x:c r="F363" s="26"/>
+      <x:c r="G363" s="29"/>
     </x:row>
     <x:row r="364">
       <x:c r="A364" s="21"/>
       <x:c r="B364" s="22"/>
       <x:c r="C364" s="14"/>
-      <x:c r="D364" s="27"/>
-      <x:c r="E364" s="27"/>
-      <x:c r="F364" s="28"/>
+      <x:c r="D364" s="26"/>
+      <x:c r="E364" s="14"/>
+      <x:c r="F364" s="26"/>
+      <x:c r="G364" s="29"/>
     </x:row>
     <x:row r="365">
       <x:c r="A365" s="21"/>
       <x:c r="B365" s="22"/>
       <x:c r="C365" s="14"/>
-      <x:c r="D365" s="27"/>
-      <x:c r="E365" s="27"/>
-      <x:c r="F365" s="28"/>
+      <x:c r="D365" s="26"/>
+      <x:c r="E365" s="14"/>
+      <x:c r="F365" s="26"/>
+      <x:c r="G365" s="29"/>
     </x:row>
     <x:row r="366">
       <x:c r="A366" s="21"/>
       <x:c r="B366" s="22"/>
       <x:c r="C366" s="14"/>
-      <x:c r="D366" s="27"/>
-      <x:c r="E366" s="27"/>
-      <x:c r="F366" s="28"/>
+      <x:c r="D366" s="26"/>
+      <x:c r="E366" s="14"/>
+      <x:c r="F366" s="26"/>
+      <x:c r="G366" s="29"/>
     </x:row>
     <x:row r="367">
       <x:c r="A367" s="21"/>
       <x:c r="B367" s="22"/>
       <x:c r="C367" s="14"/>
-      <x:c r="D367" s="27"/>
-      <x:c r="E367" s="27"/>
-      <x:c r="F367" s="28"/>
+      <x:c r="D367" s="26"/>
+      <x:c r="E367" s="14"/>
+      <x:c r="F367" s="26"/>
+      <x:c r="G367" s="29"/>
     </x:row>
     <x:row r="368">
       <x:c r="A368" s="21"/>
       <x:c r="B368" s="22"/>
       <x:c r="C368" s="14"/>
-      <x:c r="D368" s="27"/>
-      <x:c r="E368" s="27"/>
-      <x:c r="F368" s="28"/>
+      <x:c r="D368" s="26"/>
+      <x:c r="E368" s="14"/>
+      <x:c r="F368" s="26"/>
+      <x:c r="G368" s="29"/>
     </x:row>
     <x:row r="369">
       <x:c r="A369" s="21"/>
       <x:c r="B369" s="22"/>
       <x:c r="C369" s="14"/>
-      <x:c r="D369" s="27"/>
-      <x:c r="E369" s="27"/>
-      <x:c r="F369" s="28"/>
+      <x:c r="D369" s="26"/>
+      <x:c r="E369" s="14"/>
+      <x:c r="F369" s="26"/>
+      <x:c r="G369" s="29"/>
     </x:row>
     <x:row r="370">
       <x:c r="A370" s="21"/>
       <x:c r="B370" s="22"/>
       <x:c r="C370" s="14"/>
-      <x:c r="D370" s="27"/>
-      <x:c r="E370" s="27"/>
-      <x:c r="F370" s="28"/>
+      <x:c r="D370" s="26"/>
+      <x:c r="E370" s="14"/>
+      <x:c r="F370" s="26"/>
+      <x:c r="G370" s="29"/>
     </x:row>
     <x:row r="371">
       <x:c r="A371" s="21"/>
       <x:c r="B371" s="22"/>
       <x:c r="C371" s="14"/>
-      <x:c r="D371" s="27"/>
-      <x:c r="E371" s="27"/>
-      <x:c r="F371" s="28"/>
+      <x:c r="D371" s="26"/>
+      <x:c r="E371" s="14"/>
+      <x:c r="F371" s="26"/>
+      <x:c r="G371" s="29"/>
     </x:row>
     <x:row r="372">
       <x:c r="A372" s="21"/>
       <x:c r="B372" s="22"/>
       <x:c r="C372" s="14"/>
-      <x:c r="D372" s="27"/>
-      <x:c r="E372" s="27"/>
-      <x:c r="F372" s="28"/>
+      <x:c r="D372" s="26"/>
+      <x:c r="E372" s="14"/>
+      <x:c r="F372" s="26"/>
+      <x:c r="G372" s="29"/>
     </x:row>
     <x:row r="373">
       <x:c r="A373" s="21"/>
       <x:c r="B373" s="22"/>
       <x:c r="C373" s="14"/>
-      <x:c r="D373" s="27"/>
-      <x:c r="E373" s="27"/>
-      <x:c r="F373" s="28"/>
+      <x:c r="D373" s="26"/>
+      <x:c r="E373" s="14"/>
+      <x:c r="F373" s="26"/>
+      <x:c r="G373" s="29"/>
     </x:row>
     <x:row r="374">
       <x:c r="A374" s="21"/>
       <x:c r="B374" s="22"/>
       <x:c r="C374" s="14"/>
-      <x:c r="D374" s="27"/>
-      <x:c r="E374" s="27"/>
-      <x:c r="F374" s="28"/>
+      <x:c r="D374" s="26"/>
+      <x:c r="E374" s="14"/>
+      <x:c r="F374" s="26"/>
+      <x:c r="G374" s="29"/>
     </x:row>
     <x:row r="375">
       <x:c r="A375" s="21"/>
       <x:c r="B375" s="22"/>
       <x:c r="C375" s="14"/>
-      <x:c r="D375" s="27"/>
-      <x:c r="E375" s="27"/>
-      <x:c r="F375" s="28"/>
+      <x:c r="D375" s="26"/>
+      <x:c r="E375" s="14"/>
+      <x:c r="F375" s="26"/>
+      <x:c r="G375" s="29"/>
     </x:row>
     <x:row r="376">
       <x:c r="A376" s="21"/>
       <x:c r="B376" s="22"/>
       <x:c r="C376" s="14"/>
-      <x:c r="D376" s="27"/>
-      <x:c r="E376" s="27"/>
-      <x:c r="F376" s="28"/>
+      <x:c r="D376" s="26"/>
+      <x:c r="E376" s="14"/>
+      <x:c r="F376" s="26"/>
+      <x:c r="G376" s="29"/>
     </x:row>
     <x:row r="377">
       <x:c r="A377" s="21"/>
       <x:c r="B377" s="22"/>
       <x:c r="C377" s="14"/>
-      <x:c r="D377" s="27"/>
-      <x:c r="E377" s="27"/>
-      <x:c r="F377" s="28"/>
+      <x:c r="D377" s="26"/>
+      <x:c r="E377" s="14"/>
+      <x:c r="F377" s="26"/>
+      <x:c r="G377" s="29"/>
     </x:row>
     <x:row r="378">
       <x:c r="A378" s="21"/>
       <x:c r="B378" s="22"/>
       <x:c r="C378" s="14"/>
-      <x:c r="D378" s="27"/>
-      <x:c r="E378" s="27"/>
-      <x:c r="F378" s="28"/>
+      <x:c r="D378" s="26"/>
+      <x:c r="E378" s="14"/>
+      <x:c r="F378" s="26"/>
+      <x:c r="G378" s="29"/>
     </x:row>
     <x:row r="379">
       <x:c r="A379" s="21"/>
       <x:c r="B379" s="22"/>
       <x:c r="C379" s="14"/>
-      <x:c r="D379" s="27"/>
-      <x:c r="E379" s="27"/>
-      <x:c r="F379" s="28"/>
+      <x:c r="D379" s="26"/>
+      <x:c r="E379" s="14"/>
+      <x:c r="F379" s="26"/>
+      <x:c r="G379" s="29"/>
     </x:row>
     <x:row r="380">
       <x:c r="A380" s="21"/>
       <x:c r="B380" s="22"/>
       <x:c r="C380" s="14"/>
-      <x:c r="D380" s="27"/>
-      <x:c r="E380" s="27"/>
-      <x:c r="F380" s="28"/>
+      <x:c r="D380" s="26"/>
+      <x:c r="E380" s="14"/>
+      <x:c r="F380" s="26"/>
+      <x:c r="G380" s="29"/>
     </x:row>
     <x:row r="381">
       <x:c r="A381" s="21"/>
       <x:c r="B381" s="22"/>
       <x:c r="C381" s="14"/>
-      <x:c r="D381" s="27"/>
-      <x:c r="E381" s="27"/>
-      <x:c r="F381" s="28"/>
+      <x:c r="D381" s="26"/>
+      <x:c r="E381" s="14"/>
+      <x:c r="F381" s="26"/>
+      <x:c r="G381" s="29"/>
     </x:row>
     <x:row r="382">
       <x:c r="A382" s="21"/>
       <x:c r="B382" s="22"/>
       <x:c r="C382" s="14"/>
-      <x:c r="D382" s="27"/>
-      <x:c r="E382" s="27"/>
-      <x:c r="F382" s="28"/>
+      <x:c r="D382" s="26"/>
+      <x:c r="E382" s="14"/>
+      <x:c r="F382" s="26"/>
+      <x:c r="G382" s="29"/>
     </x:row>
     <x:row r="383">
       <x:c r="A383" s="21"/>
       <x:c r="B383" s="22"/>
       <x:c r="C383" s="14"/>
-      <x:c r="D383" s="27"/>
-      <x:c r="E383" s="27"/>
-      <x:c r="F383" s="28"/>
+      <x:c r="D383" s="26"/>
+      <x:c r="E383" s="14"/>
+      <x:c r="F383" s="26"/>
+      <x:c r="G383" s="29"/>
     </x:row>
     <x:row r="384">
       <x:c r="A384" s="21"/>
       <x:c r="B384" s="22"/>
       <x:c r="C384" s="14"/>
-      <x:c r="D384" s="27"/>
-      <x:c r="E384" s="27"/>
-      <x:c r="F384" s="28"/>
+      <x:c r="D384" s="26"/>
+      <x:c r="E384" s="14"/>
+      <x:c r="F384" s="26"/>
+      <x:c r="G384" s="29"/>
     </x:row>
     <x:row r="385">
       <x:c r="A385" s="21"/>
       <x:c r="B385" s="22"/>
       <x:c r="C385" s="14"/>
-      <x:c r="D385" s="27"/>
-      <x:c r="E385" s="27"/>
-      <x:c r="F385" s="28"/>
+      <x:c r="D385" s="26"/>
+      <x:c r="E385" s="14"/>
+      <x:c r="F385" s="26"/>
+      <x:c r="G385" s="29"/>
     </x:row>
     <x:row r="386">
       <x:c r="A386" s="21"/>
       <x:c r="B386" s="22"/>
       <x:c r="C386" s="14"/>
-      <x:c r="D386" s="27"/>
-      <x:c r="E386" s="27"/>
-      <x:c r="F386" s="28"/>
+      <x:c r="D386" s="26"/>
+      <x:c r="E386" s="14"/>
+      <x:c r="F386" s="26"/>
+      <x:c r="G386" s="29"/>
     </x:row>
     <x:row r="387">
       <x:c r="A387" s="21"/>
       <x:c r="B387" s="22"/>
       <x:c r="C387" s="14"/>
-      <x:c r="D387" s="27"/>
-      <x:c r="E387" s="27"/>
-      <x:c r="F387" s="28"/>
+      <x:c r="D387" s="26"/>
+      <x:c r="E387" s="14"/>
+      <x:c r="F387" s="26"/>
+      <x:c r="G387" s="29"/>
     </x:row>
     <x:row r="388">
       <x:c r="A388" s="21"/>
       <x:c r="B388" s="22"/>
       <x:c r="C388" s="14"/>
-      <x:c r="D388" s="27"/>
-      <x:c r="E388" s="27"/>
-      <x:c r="F388" s="28"/>
+      <x:c r="D388" s="26"/>
+      <x:c r="E388" s="14"/>
+      <x:c r="F388" s="26"/>
+      <x:c r="G388" s="29"/>
     </x:row>
     <x:row r="389">
       <x:c r="A389" s="21"/>
       <x:c r="B389" s="22"/>
       <x:c r="C389" s="14"/>
-      <x:c r="D389" s="27"/>
-      <x:c r="E389" s="27"/>
-      <x:c r="F389" s="28"/>
+      <x:c r="D389" s="26"/>
+      <x:c r="E389" s="14"/>
+      <x:c r="F389" s="26"/>
+      <x:c r="G389" s="29"/>
     </x:row>
     <x:row r="390">
       <x:c r="A390" s="21"/>
       <x:c r="B390" s="22"/>
       <x:c r="C390" s="14"/>
-      <x:c r="D390" s="27"/>
-      <x:c r="E390" s="27"/>
-      <x:c r="F390" s="28"/>
+      <x:c r="D390" s="26"/>
+      <x:c r="E390" s="14"/>
+      <x:c r="F390" s="26"/>
+      <x:c r="G390" s="29"/>
     </x:row>
     <x:row r="391">
       <x:c r="A391" s="21"/>
       <x:c r="B391" s="22"/>
       <x:c r="C391" s="14"/>
-      <x:c r="D391" s="27"/>
-      <x:c r="E391" s="27"/>
-      <x:c r="F391" s="28"/>
+      <x:c r="D391" s="26"/>
+      <x:c r="E391" s="14"/>
+      <x:c r="F391" s="26"/>
+      <x:c r="G391" s="29"/>
     </x:row>
     <x:row r="392">
       <x:c r="A392" s="21"/>
       <x:c r="B392" s="22"/>
       <x:c r="C392" s="14"/>
-      <x:c r="D392" s="27"/>
-      <x:c r="E392" s="27"/>
-      <x:c r="F392" s="28"/>
+      <x:c r="D392" s="26"/>
+      <x:c r="E392" s="14"/>
+      <x:c r="F392" s="26"/>
+      <x:c r="G392" s="29"/>
     </x:row>
     <x:row r="393">
       <x:c r="A393" s="21"/>
       <x:c r="B393" s="22"/>
       <x:c r="C393" s="14"/>
-      <x:c r="D393" s="27"/>
-      <x:c r="E393" s="27"/>
-      <x:c r="F393" s="28"/>
+      <x:c r="D393" s="26"/>
+      <x:c r="E393" s="14"/>
+      <x:c r="F393" s="26"/>
+      <x:c r="G393" s="29"/>
     </x:row>
     <x:row r="394">
       <x:c r="A394" s="21"/>
       <x:c r="B394" s="22"/>
       <x:c r="C394" s="14"/>
-      <x:c r="D394" s="27"/>
-      <x:c r="E394" s="27"/>
-      <x:c r="F394" s="28"/>
+      <x:c r="D394" s="26"/>
+      <x:c r="E394" s="14"/>
+      <x:c r="F394" s="26"/>
+      <x:c r="G394" s="29"/>
     </x:row>
     <x:row r="395">
       <x:c r="A395" s="21"/>
       <x:c r="B395" s="22"/>
       <x:c r="C395" s="14"/>
-      <x:c r="D395" s="27"/>
-      <x:c r="E395" s="27"/>
-      <x:c r="F395" s="28"/>
+      <x:c r="D395" s="26"/>
+      <x:c r="E395" s="14"/>
+      <x:c r="F395" s="26"/>
+      <x:c r="G395" s="29"/>
     </x:row>
     <x:row r="396">
       <x:c r="A396" s="21"/>
       <x:c r="B396" s="22"/>
       <x:c r="C396" s="14"/>
-      <x:c r="D396" s="27"/>
-      <x:c r="E396" s="27"/>
-      <x:c r="F396" s="28"/>
+      <x:c r="D396" s="26"/>
+      <x:c r="E396" s="14"/>
+      <x:c r="F396" s="26"/>
+      <x:c r="G396" s="29"/>
     </x:row>
     <x:row r="397">
       <x:c r="A397" s="21"/>
       <x:c r="B397" s="22"/>
       <x:c r="C397" s="14"/>
-      <x:c r="D397" s="27"/>
-      <x:c r="E397" s="27"/>
-      <x:c r="F397" s="28"/>
+      <x:c r="D397" s="26"/>
+      <x:c r="E397" s="14"/>
+      <x:c r="F397" s="26"/>
+      <x:c r="G397" s="29"/>
     </x:row>
     <x:row r="398">
       <x:c r="A398" s="21"/>
       <x:c r="B398" s="22"/>
       <x:c r="C398" s="14"/>
-      <x:c r="D398" s="27"/>
-      <x:c r="E398" s="27"/>
-      <x:c r="F398" s="28"/>
+      <x:c r="D398" s="26"/>
+      <x:c r="E398" s="14"/>
+      <x:c r="F398" s="26"/>
+      <x:c r="G398" s="29"/>
     </x:row>
     <x:row r="399">
       <x:c r="A399" s="21"/>
       <x:c r="B399" s="22"/>
       <x:c r="C399" s="14"/>
-      <x:c r="D399" s="27"/>
-      <x:c r="E399" s="27"/>
-      <x:c r="F399" s="28"/>
+      <x:c r="D399" s="26"/>
+      <x:c r="E399" s="14"/>
+      <x:c r="F399" s="26"/>
+      <x:c r="G399" s="29"/>
     </x:row>
     <x:row r="400">
       <x:c r="A400" s="21"/>
       <x:c r="B400" s="22"/>
       <x:c r="C400" s="14"/>
-      <x:c r="D400" s="27"/>
-      <x:c r="E400" s="27"/>
-      <x:c r="F400" s="28"/>
+      <x:c r="D400" s="26"/>
+      <x:c r="E400" s="14"/>
+      <x:c r="F400" s="26"/>
+      <x:c r="G400" s="29"/>
     </x:row>
     <x:row r="401">
       <x:c r="A401" s="23"/>
       <x:c r="B401" s="24"/>
       <x:c r="C401" s="17"/>
-      <x:c r="D401" s="29"/>
-      <x:c r="E401" s="29"/>
-      <x:c r="F401" s="30"/>
+      <x:c r="D401" s="27"/>
+      <x:c r="E401" s="17"/>
+      <x:c r="F401" s="27"/>
+      <x:c r="G401" s="30"/>
     </x:row>
   </x:sheetData>
-  <x:dataValidations count="3">
+  <x:dataValidations count="4">
     <x:dataValidation type="list" sqref="C2:C401">
       <x:formula1>"Female,Male,Intersex,Unknown/not recorded"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="whole" operator="between" sqref="D2:D401">
       <x:formula1>0</x:formula1>
-      <x:formula2>60</x:formula2>
+      <x:formula2>1826</x:formula2>
     </x:dataValidation>
-    <x:dataValidation type="whole" operator="between" sqref="E2:F401">
+    <x:dataValidation type="list" sqref="E2:E401">
+      <x:formula1>"Yes,No"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="between" sqref="F2:G401">
       <x:formula1>0</x:formula1>
       <x:formula2>3650</x:formula2>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R17fd4bee6cc34afc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2c89ea5b32ba458a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3785,44 +4200,52 @@
         <x:v>Select the clinic-recorded category from the dropdown.</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="15" hidden="0" customHeight="1">
+    <x:row r="8" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A8" s="37" t="str">
-        <x:v>age_at_onset_months</x:v>
+        <x:v>age_at_onset_days</x:v>
       </x:c>
       <x:c r="B8" s="38" t="str">
-        <x:v>Age in completed months on the locally determined onset date.</x:v>
+        <x:v>Age in whole days on the locally determined parent-recognized onset date, calculated locally without transmitting birth or onset dates.</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="15" hidden="0" customHeight="1">
+    <x:row r="9" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A9" s="37" t="str">
+        <x:v>vaccination_before_onset</x:v>
+      </x:c>
+      <x:c r="B9" s="38" t="str">
+        <x:v>Yes only with a documented administration before/on onset; No only with sufficient records documenting no prior vaccination. Never treat incomplete history as No.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" s="37" t="str">
         <x:v>dpre_days</x:v>
       </x:c>
-      <x:c r="B9" s="38" t="str">
+      <x:c r="B10" s="38" t="str">
         <x:v>Calendar days from the most recent administered vaccination before/on onset to onset. Same day = 0.</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="15" hidden="0" customHeight="1">
-      <x:c r="A10" s="37" t="str">
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11" s="37" t="str">
         <x:v>dpost_days</x:v>
       </x:c>
-      <x:c r="B10" s="38" t="str">
+      <x:c r="B11" s="38" t="str">
         <x:v>Calendar days from onset to the first administered vaccination after onset.</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A11" s="37" t="str">
+    <x:row r="12" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A12" s="37" t="str">
         <x:v>Prohibited</x:v>
       </x:c>
-      <x:c r="B11" s="38" t="str">
+      <x:c r="B12" s="38" t="str">
         <x:v>No calendar dates, phenotype information, narrative/free text, patient names, MRNs, contact data, geography, clinic name, or patient mapping key.</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A12" s="37" t="str">
+    <x:row r="13" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A13" s="37" t="str">
         <x:v>Certification</x:v>
       </x:c>
-      <x:c r="B12" s="38" t="str">
-        <x:v>The uploading clinic certifies that eligibility was verified locally and the electronic file contains only the six approved data fields.</x:v>
+      <x:c r="B13" s="38" t="str">
+        <x:v>The uploading clinic certifies that eligibility was verified locally and the electronic file contains only the seven approved patient-level fields plus separately labeled aggregate counts.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3831,4 +4254,63 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="85" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="15" hidden="0" customHeight="1">
+      <x:c r="A1" s="39" t="str">
+        <x:v>site_code</x:v>
+      </x:c>
+      <x:c r="B1" s="39" t="str">
+        <x:v>aggregate_measure</x:v>
+      </x:c>
+      <x:c r="C1" s="39" t="str">
+        <x:v>count</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="15" hidden="0" customHeight="1">
+      <x:c r="A2" s="40"/>
+      <x:c r="B2" s="40" t="str">
+        <x:v>All clinic patients with sufficient records to establish vaccination status through 24 months</x:v>
+      </x:c>
+      <x:c r="C2" s="40"/>
+    </x:row>
+    <x:row r="3" ht="15" hidden="0" customHeight="1">
+      <x:c r="A3" s="40"/>
+      <x:c r="B3" s="40" t="str">
+        <x:v>Above patients with no documented vaccination through 24 months</x:v>
+      </x:c>
+      <x:c r="C3" s="40"/>
+    </x:row>
+    <x:row r="4" ht="15" hidden="0" customHeight="1">
+      <x:c r="A4" s="40"/>
+      <x:c r="B4" s="40" t="str">
+        <x:v>Qualifying SORA cases with sufficient records to establish vaccination status through 24 months</x:v>
+      </x:c>
+      <x:c r="C4" s="40"/>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="40"/>
+      <x:c r="B5" s="40" t="str">
+        <x:v>Above SORA cases with no documented vaccination through 24 months</x:v>
+      </x:c>
+      <x:c r="C5" s="40"/>
+    </x:row>
+  </x:sheetData>
+  <x:dataValidations count="1">
+    <x:dataValidation type="whole" operator="between" sqref="C2:C5">
+      <x:formula1>0</x:formula1>
+      <x:formula2>10000000</x:formula2>
+    </x:dataValidation>
+  </x:dataValidations>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>
--- a/irb_submission/IRB_SUBMISSION_BUNDLE/03_SORA_Electronic_Data_Submission_Template.xlsx
+++ b/irb_submission/IRB_SUBMISSION_BUNDLE/03_SORA_Electronic_Data_Submission_Template.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Entry" sheetId="1" r:id="R92ecf88bc42343e8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="2" r:id="R563e1ce891b44394"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Site Summary" sheetId="3" r:id="R2f881b4ea8214977"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Entry" sheetId="1" r:id="R61091b71b4c34e18"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="2" r:id="R268efd854e0d46ea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Site Summary" sheetId="3" r:id="Rf8eeec418a0844e6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4139,7 +4139,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2c89ea5b32ba458a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7491f89b725848e2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4176,12 +4176,12 @@
         <x:v>Enter one eligible patient per row. Do not add columns.</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="15" hidden="0" customHeight="1">
+    <x:row r="5" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A5" s="37" t="str">
         <x:v>site_code</x:v>
       </x:c>
       <x:c r="B5" s="38" t="str">
-        <x:v>Use the nonidentifying site code assigned for this study (for example, SITE01). Do not enter the clinic name.</x:v>
+        <x:v>Use the study site code assigned for analysis (for example, SITE01). Do not enter the clinic name; the clinic-code mapping is stored separately with restricted access.</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="26.399999618530273" hidden="0" customHeight="1">
